--- a/products.xlsx
+++ b/products.xlsx
@@ -7790,7 +7790,11 @@
       <c r="H204" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I204" s="2" t="n"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>102966.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -8019,7 +8023,11 @@
         </is>
       </c>
       <c r="H211" s="3" t="n"/>
-      <c r="I211" s="2" t="n"/>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>109703.png</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -8052,7 +8060,11 @@
       <c r="H212" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="I212" s="2" t="n"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>100226.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8085,7 +8097,11 @@
       <c r="H213" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I213" s="2" t="n"/>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>110928.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -8116,7 +8132,11 @@
         </is>
       </c>
       <c r="H214" s="3" t="n"/>
-      <c r="I214" s="2" t="n"/>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>108504.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -8302,7 +8322,11 @@
         </is>
       </c>
       <c r="H220" s="3" t="n"/>
-      <c r="I220" s="2" t="n"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>113519.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -8333,7 +8357,11 @@
         </is>
       </c>
       <c r="H221" s="3" t="n"/>
-      <c r="I221" s="2" t="n"/>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>108976.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -8364,7 +8392,11 @@
         </is>
       </c>
       <c r="H222" s="3" t="n"/>
-      <c r="I222" s="2" t="n"/>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>108975.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -8395,7 +8427,11 @@
         </is>
       </c>
       <c r="H223" s="3" t="n"/>
-      <c r="I223" s="2" t="n"/>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>108406.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -8612,7 +8648,11 @@
         </is>
       </c>
       <c r="H230" s="3" t="n"/>
-      <c r="I230" s="2" t="n"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>113553.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -8953,7 +8993,11 @@
         </is>
       </c>
       <c r="H241" s="3" t="n"/>
-      <c r="I241" s="2" t="n"/>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>102614.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -8984,7 +9028,11 @@
         </is>
       </c>
       <c r="H242" s="3" t="n"/>
-      <c r="I242" s="2" t="n"/>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>102615.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -9015,7 +9063,11 @@
         </is>
       </c>
       <c r="H243" s="3" t="n"/>
-      <c r="I243" s="2" t="n"/>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>102616.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -9046,7 +9098,11 @@
         </is>
       </c>
       <c r="H244" s="3" t="n"/>
-      <c r="I244" s="2" t="n"/>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>102617.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -9077,7 +9133,11 @@
         </is>
       </c>
       <c r="H245" s="3" t="n"/>
-      <c r="I245" s="2" t="n"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>102618.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -9108,7 +9168,11 @@
         </is>
       </c>
       <c r="H246" s="3" t="n"/>
-      <c r="I246" s="2" t="n"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>102619.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -9201,7 +9265,11 @@
         </is>
       </c>
       <c r="H249" s="3" t="n"/>
-      <c r="I249" s="2" t="n"/>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>102750.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -9232,7 +9300,11 @@
         </is>
       </c>
       <c r="H250" s="3" t="n"/>
-      <c r="I250" s="2" t="n"/>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>102763.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -9263,7 +9335,11 @@
         </is>
       </c>
       <c r="H251" s="3" t="n"/>
-      <c r="I251" s="2" t="n"/>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>107790.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -9387,7 +9463,11 @@
         </is>
       </c>
       <c r="H255" s="3" t="n"/>
-      <c r="I255" s="2" t="n"/>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>110750.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -9418,7 +9498,11 @@
         </is>
       </c>
       <c r="H256" s="3" t="n"/>
-      <c r="I256" s="2" t="n"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>106513.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -9480,7 +9564,11 @@
         </is>
       </c>
       <c r="H258" s="3" t="n"/>
-      <c r="I258" s="2" t="n"/>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>109507.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -9511,7 +9599,11 @@
         </is>
       </c>
       <c r="H259" s="3" t="n"/>
-      <c r="I259" s="2" t="n"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>102168.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -9542,7 +9634,11 @@
         </is>
       </c>
       <c r="H260" s="3" t="n"/>
-      <c r="I260" s="2" t="n"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>103250.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -9573,7 +9669,11 @@
         </is>
       </c>
       <c r="H261" s="3" t="n"/>
-      <c r="I261" s="2" t="n"/>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>108179.png</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -9604,7 +9704,11 @@
         </is>
       </c>
       <c r="H262" s="3" t="n"/>
-      <c r="I262" s="2" t="n"/>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>104423.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -9635,7 +9739,11 @@
         </is>
       </c>
       <c r="H263" s="3" t="n"/>
-      <c r="I263" s="2" t="n"/>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>104424.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -9666,7 +9774,11 @@
         </is>
       </c>
       <c r="H264" s="3" t="n"/>
-      <c r="I264" s="2" t="n"/>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>104427.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -9697,7 +9809,11 @@
         </is>
       </c>
       <c r="H265" s="3" t="n"/>
-      <c r="I265" s="2" t="n"/>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>104426.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -9728,7 +9844,11 @@
         </is>
       </c>
       <c r="H266" s="3" t="n"/>
-      <c r="I266" s="2" t="n"/>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>104435.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -9790,7 +9910,11 @@
         </is>
       </c>
       <c r="H268" s="3" t="n"/>
-      <c r="I268" s="2" t="n"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>104439.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -9821,7 +9945,11 @@
         </is>
       </c>
       <c r="H269" s="3" t="n"/>
-      <c r="I269" s="2" t="n"/>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>104447.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -9852,7 +9980,11 @@
         </is>
       </c>
       <c r="H270" s="3" t="n"/>
-      <c r="I270" s="2" t="n"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>104446.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -9883,7 +10015,11 @@
         </is>
       </c>
       <c r="H271" s="3" t="n"/>
-      <c r="I271" s="2" t="n"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>104442.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -9914,7 +10050,11 @@
         </is>
       </c>
       <c r="H272" s="3" t="n"/>
-      <c r="I272" s="2" t="n"/>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>108242.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -9945,7 +10085,11 @@
         </is>
       </c>
       <c r="H273" s="3" t="n"/>
-      <c r="I273" s="2" t="n"/>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>105662.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -9976,7 +10120,11 @@
         </is>
       </c>
       <c r="H274" s="3" t="n"/>
-      <c r="I274" s="2" t="n"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>100966.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -10007,7 +10155,11 @@
         </is>
       </c>
       <c r="H275" s="3" t="n"/>
-      <c r="I275" s="2" t="n"/>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>107373.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -10038,7 +10190,11 @@
         </is>
       </c>
       <c r="H276" s="3" t="n"/>
-      <c r="I276" s="2" t="n"/>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>100969.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -10069,7 +10225,11 @@
         </is>
       </c>
       <c r="H277" s="3" t="n"/>
-      <c r="I277" s="2" t="n"/>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>106499.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -10100,7 +10260,11 @@
         </is>
       </c>
       <c r="H278" s="3" t="n"/>
-      <c r="I278" s="2" t="n"/>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>100987.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -10131,7 +10295,11 @@
         </is>
       </c>
       <c r="H279" s="3" t="n"/>
-      <c r="I279" s="2" t="n"/>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>106369.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -10162,7 +10330,11 @@
         </is>
       </c>
       <c r="H280" s="3" t="n"/>
-      <c r="I280" s="2" t="n"/>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>100998.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -10193,7 +10365,11 @@
         </is>
       </c>
       <c r="H281" s="3" t="n"/>
-      <c r="I281" s="2" t="n"/>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>108664.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -10224,7 +10400,11 @@
         </is>
       </c>
       <c r="H282" s="3" t="n"/>
-      <c r="I282" s="2" t="n"/>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>105736.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -10255,7 +10435,11 @@
         </is>
       </c>
       <c r="H283" s="3" t="n"/>
-      <c r="I283" s="2" t="n"/>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>108083.png</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -10286,7 +10470,11 @@
         </is>
       </c>
       <c r="H284" s="3" t="n"/>
-      <c r="I284" s="2" t="n"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>100957.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -10317,7 +10505,11 @@
         </is>
       </c>
       <c r="H285" s="3" t="n"/>
-      <c r="I285" s="2" t="n"/>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>105823.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -10348,7 +10540,11 @@
         </is>
       </c>
       <c r="H286" s="3" t="n"/>
-      <c r="I286" s="2" t="n"/>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>102716.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -10379,7 +10575,11 @@
         </is>
       </c>
       <c r="H287" s="3" t="n"/>
-      <c r="I287" s="2" t="n"/>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>103163.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -10410,7 +10610,11 @@
         </is>
       </c>
       <c r="H288" s="3" t="n"/>
-      <c r="I288" s="2" t="n"/>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>103257.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -10441,7 +10645,11 @@
         </is>
       </c>
       <c r="H289" s="3" t="n"/>
-      <c r="I289" s="2" t="n"/>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>105755.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -10472,7 +10680,11 @@
         </is>
       </c>
       <c r="H290" s="3" t="n"/>
-      <c r="I290" s="2" t="n"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>107554.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -10503,7 +10715,11 @@
         </is>
       </c>
       <c r="H291" s="3" t="n"/>
-      <c r="I291" s="2" t="n"/>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>108384.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -10534,7 +10750,11 @@
         </is>
       </c>
       <c r="H292" s="3" t="n"/>
-      <c r="I292" s="2" t="n"/>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>108385.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -10565,7 +10785,11 @@
         </is>
       </c>
       <c r="H293" s="3" t="n"/>
-      <c r="I293" s="2" t="n"/>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>108386.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -10596,7 +10820,11 @@
         </is>
       </c>
       <c r="H294" s="3" t="n"/>
-      <c r="I294" s="2" t="n"/>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>109044.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -10627,7 +10855,11 @@
         </is>
       </c>
       <c r="H295" s="3" t="n"/>
-      <c r="I295" s="2" t="n"/>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>110610.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -10658,7 +10890,11 @@
         </is>
       </c>
       <c r="H296" s="3" t="n"/>
-      <c r="I296" s="2" t="n"/>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>108954.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -10689,7 +10925,11 @@
         </is>
       </c>
       <c r="H297" s="3" t="n"/>
-      <c r="I297" s="2" t="n"/>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>113996.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -10720,7 +10960,11 @@
         </is>
       </c>
       <c r="H298" s="3" t="n"/>
-      <c r="I298" s="2" t="n"/>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>110936.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -10751,7 +10995,11 @@
         </is>
       </c>
       <c r="H299" s="3" t="n"/>
-      <c r="I299" s="2" t="n"/>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>109036.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -10782,7 +11030,11 @@
         </is>
       </c>
       <c r="H300" s="3" t="n"/>
-      <c r="I300" s="2" t="n"/>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>108158.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -10813,7 +11065,11 @@
         </is>
       </c>
       <c r="H301" s="3" t="n"/>
-      <c r="I301" s="2" t="n"/>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>108948.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -10844,7 +11100,11 @@
         </is>
       </c>
       <c r="H302" s="3" t="n"/>
-      <c r="I302" s="2" t="n"/>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>110342.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -10875,7 +11135,11 @@
         </is>
       </c>
       <c r="H303" s="3" t="n"/>
-      <c r="I303" s="2" t="n"/>
+      <c r="I303" s="2" t="inlineStr">
+        <is>
+          <t>110046.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -10906,7 +11170,11 @@
         </is>
       </c>
       <c r="H304" s="3" t="n"/>
-      <c r="I304" s="2" t="n"/>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>110503.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -10937,7 +11205,11 @@
         </is>
       </c>
       <c r="H305" s="3" t="n"/>
-      <c r="I305" s="2" t="n"/>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>107961.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -10968,7 +11240,11 @@
         </is>
       </c>
       <c r="H306" s="3" t="n"/>
-      <c r="I306" s="2" t="n"/>
+      <c r="I306" s="2" t="inlineStr">
+        <is>
+          <t>102176.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -10999,7 +11275,11 @@
         </is>
       </c>
       <c r="H307" s="3" t="n"/>
-      <c r="I307" s="2" t="n"/>
+      <c r="I307" s="2" t="inlineStr">
+        <is>
+          <t>107960.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -11030,7 +11310,11 @@
         </is>
       </c>
       <c r="H308" s="3" t="n"/>
-      <c r="I308" s="2" t="n"/>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>102189.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -11061,7 +11345,11 @@
         </is>
       </c>
       <c r="H309" s="3" t="n"/>
-      <c r="I309" s="2" t="n"/>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>102139.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -11092,7 +11380,11 @@
         </is>
       </c>
       <c r="H310" s="3" t="n"/>
-      <c r="I310" s="2" t="n"/>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>102141.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -11123,7 +11415,11 @@
         </is>
       </c>
       <c r="H311" s="3" t="n"/>
-      <c r="I311" s="2" t="n"/>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>102145.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -11154,7 +11450,11 @@
         </is>
       </c>
       <c r="H312" s="3" t="n"/>
-      <c r="I312" s="2" t="n"/>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>102146.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -11185,7 +11485,11 @@
         </is>
       </c>
       <c r="H313" s="3" t="n"/>
-      <c r="I313" s="2" t="n"/>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>102223.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -11216,7 +11520,11 @@
         </is>
       </c>
       <c r="H314" s="3" t="n"/>
-      <c r="I314" s="2" t="n"/>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>102150.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -11247,7 +11555,11 @@
         </is>
       </c>
       <c r="H315" s="3" t="n"/>
-      <c r="I315" s="2" t="n"/>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>109422.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -11278,7 +11590,11 @@
         </is>
       </c>
       <c r="H316" s="3" t="n"/>
-      <c r="I316" s="2" t="n"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>108211.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -11309,7 +11625,11 @@
         </is>
       </c>
       <c r="H317" s="3" t="n"/>
-      <c r="I317" s="2" t="n"/>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>102151.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -11340,7 +11660,11 @@
         </is>
       </c>
       <c r="H318" s="3" t="n"/>
-      <c r="I318" s="2" t="n"/>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>102152.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -11371,7 +11695,11 @@
         </is>
       </c>
       <c r="H319" s="3" t="n"/>
-      <c r="I319" s="2" t="n"/>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>102154.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -11402,7 +11730,11 @@
         </is>
       </c>
       <c r="H320" s="3" t="n"/>
-      <c r="I320" s="2" t="n"/>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>102158.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -11433,7 +11765,11 @@
         </is>
       </c>
       <c r="H321" s="3" t="n"/>
-      <c r="I321" s="2" t="n"/>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>102159.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -11464,7 +11800,11 @@
         </is>
       </c>
       <c r="H322" s="3" t="n"/>
-      <c r="I322" s="2" t="n"/>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>102193.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -11495,7 +11835,11 @@
         </is>
       </c>
       <c r="H323" s="3" t="n"/>
-      <c r="I323" s="2" t="n"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>108079.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -11526,7 +11870,11 @@
         </is>
       </c>
       <c r="H324" s="3" t="n"/>
-      <c r="I324" s="2" t="n"/>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>102165.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -11557,7 +11905,11 @@
         </is>
       </c>
       <c r="H325" s="3" t="n"/>
-      <c r="I325" s="2" t="n"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>108084.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -11588,7 +11940,11 @@
         </is>
       </c>
       <c r="H326" s="3" t="n"/>
-      <c r="I326" s="2" t="n"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>102177.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -11619,7 +11975,11 @@
         </is>
       </c>
       <c r="H327" s="3" t="n"/>
-      <c r="I327" s="2" t="n"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>102173.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -11650,7 +12010,11 @@
         </is>
       </c>
       <c r="H328" s="3" t="n"/>
-      <c r="I328" s="2" t="n"/>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>102170.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -11681,7 +12045,11 @@
         </is>
       </c>
       <c r="H329" s="3" t="n"/>
-      <c r="I329" s="2" t="n"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>105165.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -11712,7 +12080,11 @@
         </is>
       </c>
       <c r="H330" s="3" t="n"/>
-      <c r="I330" s="2" t="n"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>102065.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -11826,7 +12198,11 @@
         </is>
       </c>
       <c r="H334" s="3" t="n"/>
-      <c r="I334" s="2" t="n"/>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>102125.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="n">
@@ -11855,7 +12231,11 @@
         </is>
       </c>
       <c r="H335" s="3" t="n"/>
-      <c r="I335" s="2" t="n"/>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>109031.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -11884,7 +12264,11 @@
         </is>
       </c>
       <c r="H336" s="3" t="n"/>
-      <c r="I336" s="2" t="n"/>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>107594.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -11913,7 +12297,11 @@
         </is>
       </c>
       <c r="H337" s="3" t="n"/>
-      <c r="I337" s="2" t="n"/>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>102223.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -11942,7 +12330,11 @@
         </is>
       </c>
       <c r="H338" s="3" t="n"/>
-      <c r="I338" s="2" t="n"/>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>102195.png</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -11971,7 +12363,11 @@
         </is>
       </c>
       <c r="H339" s="3" t="n"/>
-      <c r="I339" s="2" t="n"/>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>109034.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -12000,7 +12396,11 @@
         </is>
       </c>
       <c r="H340" s="3" t="n"/>
-      <c r="I340" s="2" t="n"/>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>102066.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -12029,7 +12429,11 @@
         </is>
       </c>
       <c r="H341" s="3" t="n"/>
-      <c r="I341" s="2" t="n"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>108210.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -12058,7 +12462,11 @@
         </is>
       </c>
       <c r="H342" s="3" t="n"/>
-      <c r="I342" s="2" t="n"/>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>102068.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -12087,7 +12495,11 @@
         </is>
       </c>
       <c r="H343" s="3" t="n"/>
-      <c r="I343" s="2" t="n"/>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>102067.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -12645,7 +13057,11 @@
         </is>
       </c>
       <c r="H361" s="3" t="n"/>
-      <c r="I361" s="2" t="n"/>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>100942.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -12676,7 +13092,11 @@
         </is>
       </c>
       <c r="H362" s="3" t="n"/>
-      <c r="I362" s="2" t="n"/>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>100942.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -12707,7 +13127,11 @@
         </is>
       </c>
       <c r="H363" s="3" t="n"/>
-      <c r="I363" s="2" t="n"/>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>109885.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -12862,7 +13286,11 @@
         </is>
       </c>
       <c r="H368" s="3" t="n"/>
-      <c r="I368" s="2" t="n"/>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>100937.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -13985,7 +14413,11 @@
         </is>
       </c>
       <c r="H405" s="3" t="n"/>
-      <c r="I405" s="2" t="n"/>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>100402.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -14171,7 +14603,11 @@
         </is>
       </c>
       <c r="H411" s="3" t="n"/>
-      <c r="I411" s="2" t="n"/>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>108689.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -14202,7 +14638,11 @@
         </is>
       </c>
       <c r="H412" s="3" t="n"/>
-      <c r="I412" s="2" t="n"/>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>108689.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -14264,7 +14704,11 @@
         </is>
       </c>
       <c r="H414" s="3" t="n"/>
-      <c r="I414" s="2" t="n"/>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>100248.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -14295,7 +14739,11 @@
         </is>
       </c>
       <c r="H415" s="3" t="n"/>
-      <c r="I415" s="2" t="n"/>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>100249.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -14574,7 +15022,11 @@
         </is>
       </c>
       <c r="H424" s="3" t="n"/>
-      <c r="I424" s="2" t="n"/>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>100060.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -14605,7 +15057,11 @@
         </is>
       </c>
       <c r="H425" s="3" t="n"/>
-      <c r="I425" s="2" t="n"/>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>100061.jpeg</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -14636,7 +15092,11 @@
         </is>
       </c>
       <c r="H426" s="3" t="n"/>
-      <c r="I426" s="2" t="n"/>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>100059.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -14729,7 +15189,11 @@
         </is>
       </c>
       <c r="H429" s="3" t="n"/>
-      <c r="I429" s="2" t="n"/>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>113519.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -14760,7 +15224,11 @@
         </is>
       </c>
       <c r="H430" s="3" t="n"/>
-      <c r="I430" s="2" t="n"/>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>113518.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -14791,7 +15259,11 @@
         </is>
       </c>
       <c r="H431" s="3" t="n"/>
-      <c r="I431" s="2" t="n"/>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>100000.JPG</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -14822,7 +15294,11 @@
         </is>
       </c>
       <c r="H432" s="3" t="n"/>
-      <c r="I432" s="2" t="n"/>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>100003.png</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -14884,7 +15360,11 @@
         </is>
       </c>
       <c r="H434" s="3" t="n"/>
-      <c r="I434" s="2" t="n"/>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>100571.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -15101,7 +15581,11 @@
         </is>
       </c>
       <c r="H441" s="3" t="n"/>
-      <c r="I441" s="2" t="n"/>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>108975.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -15132,7 +15616,11 @@
         </is>
       </c>
       <c r="H442" s="3" t="n"/>
-      <c r="I442" s="2" t="n"/>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>108976.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -15163,7 +15651,11 @@
         </is>
       </c>
       <c r="H443" s="3" t="n"/>
-      <c r="I443" s="2" t="n"/>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>108406.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -15194,7 +15686,11 @@
         </is>
       </c>
       <c r="H444" s="3" t="n"/>
-      <c r="I444" s="2" t="n"/>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>100230.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -15225,7 +15721,11 @@
         </is>
       </c>
       <c r="H445" s="3" t="n"/>
-      <c r="I445" s="2" t="n"/>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>106393.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">

--- a/products.xlsx
+++ b/products.xlsx
@@ -7757,7 +7757,11 @@
       <c r="H203" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I203" s="2" t="n"/>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>112569.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -7827,7 +7831,11 @@
       <c r="H205" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="I205" s="2" t="n"/>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>111970.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7860,7 +7868,11 @@
       <c r="H206" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I206" s="2" t="n"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>112571.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -7893,7 +7905,11 @@
       <c r="H207" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I207" s="2" t="n"/>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>112571.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -7926,7 +7942,11 @@
       <c r="H208" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I208" s="2" t="n"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>115016.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -7959,7 +7979,11 @@
       <c r="H209" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I209" s="2" t="n"/>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>115271.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -7992,7 +8016,11 @@
       <c r="H210" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="I210" s="2" t="n"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>114919.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -8167,7 +8195,11 @@
         </is>
       </c>
       <c r="H215" s="3" t="n"/>
-      <c r="I215" s="2" t="n"/>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>100583.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -8198,7 +8230,11 @@
         </is>
       </c>
       <c r="H216" s="3" t="n"/>
-      <c r="I216" s="2" t="n"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>108362.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -8229,7 +8265,11 @@
         </is>
       </c>
       <c r="H217" s="3" t="n"/>
-      <c r="I217" s="2" t="n"/>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>115769.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -8260,7 +8300,11 @@
         </is>
       </c>
       <c r="H218" s="3" t="n"/>
-      <c r="I218" s="2" t="n"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>108364.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -8291,7 +8335,11 @@
         </is>
       </c>
       <c r="H219" s="3" t="n"/>
-      <c r="I219" s="2" t="n"/>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>108365.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -8462,7 +8510,11 @@
         </is>
       </c>
       <c r="H224" s="3" t="n"/>
-      <c r="I224" s="2" t="n"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>114956.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -8493,7 +8545,11 @@
         </is>
       </c>
       <c r="H225" s="3" t="n"/>
-      <c r="I225" s="2" t="n"/>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>115172.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8524,7 +8580,11 @@
         </is>
       </c>
       <c r="H226" s="3" t="n"/>
-      <c r="I226" s="2" t="n"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>112593.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -8555,7 +8615,11 @@
         </is>
       </c>
       <c r="H227" s="3" t="n"/>
-      <c r="I227" s="2" t="n"/>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>112591.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -8586,7 +8650,11 @@
         </is>
       </c>
       <c r="H228" s="3" t="n"/>
-      <c r="I228" s="2" t="n"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>112594.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -8617,7 +8685,11 @@
         </is>
       </c>
       <c r="H229" s="3" t="n"/>
-      <c r="I229" s="2" t="n"/>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>112592.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8683,7 +8755,11 @@
         </is>
       </c>
       <c r="H231" s="3" t="n"/>
-      <c r="I231" s="2" t="n"/>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>115275.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8714,7 +8790,11 @@
         </is>
       </c>
       <c r="H232" s="3" t="n"/>
-      <c r="I232" s="2" t="n"/>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>115277.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -8745,7 +8825,11 @@
         </is>
       </c>
       <c r="H233" s="3" t="n"/>
-      <c r="I233" s="2" t="n"/>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>114990.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -8776,7 +8860,11 @@
         </is>
       </c>
       <c r="H234" s="3" t="n"/>
-      <c r="I234" s="2" t="n"/>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>115274.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -8807,7 +8895,11 @@
         </is>
       </c>
       <c r="H235" s="3" t="n"/>
-      <c r="I235" s="2" t="n"/>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>113359.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -8838,7 +8930,11 @@
         </is>
       </c>
       <c r="H236" s="3" t="n"/>
-      <c r="I236" s="2" t="n"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>114364.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -8869,7 +8965,11 @@
         </is>
       </c>
       <c r="H237" s="3" t="n"/>
-      <c r="I237" s="2" t="n"/>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>114365.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -8900,7 +9000,11 @@
         </is>
       </c>
       <c r="H238" s="3" t="n"/>
-      <c r="I238" s="2" t="n"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>113360.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -8931,7 +9035,11 @@
         </is>
       </c>
       <c r="H239" s="3" t="n"/>
-      <c r="I239" s="2" t="n"/>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>114449.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -8962,7 +9070,11 @@
         </is>
       </c>
       <c r="H240" s="3" t="n"/>
-      <c r="I240" s="2" t="n"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>114451.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -9203,7 +9315,11 @@
         </is>
       </c>
       <c r="H247" s="3" t="n"/>
-      <c r="I247" s="2" t="n"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>102763.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -9234,7 +9350,11 @@
         </is>
       </c>
       <c r="H248" s="3" t="n"/>
-      <c r="I248" s="2" t="n"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>102750.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -9879,7 +9999,11 @@
         </is>
       </c>
       <c r="H267" s="3" t="n"/>
-      <c r="I267" s="2" t="n"/>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>104438.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -12530,7 +12654,11 @@
         </is>
       </c>
       <c r="H344" s="3" t="n"/>
-      <c r="I344" s="2" t="n"/>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>111181.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -12561,7 +12689,11 @@
         </is>
       </c>
       <c r="H345" s="3" t="n"/>
-      <c r="I345" s="2" t="n"/>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>111175.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -12592,7 +12724,11 @@
         </is>
       </c>
       <c r="H346" s="3" t="n"/>
-      <c r="I346" s="2" t="n"/>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>111147.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="347" ht="15" customHeight="1">
       <c r="A347" s="2" t="inlineStr">
@@ -12623,7 +12759,11 @@
         </is>
       </c>
       <c r="H347" s="3" t="n"/>
-      <c r="I347" s="2" t="n"/>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>111201.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -12654,7 +12794,11 @@
         </is>
       </c>
       <c r="H348" s="3" t="n"/>
-      <c r="I348" s="2" t="n"/>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>111185.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -12685,7 +12829,11 @@
         </is>
       </c>
       <c r="H349" s="3" t="n"/>
-      <c r="I349" s="2" t="n"/>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>111995.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -12716,7 +12864,11 @@
         </is>
       </c>
       <c r="H350" s="3" t="n"/>
-      <c r="I350" s="2" t="n"/>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>111149.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -12747,7 +12899,11 @@
         </is>
       </c>
       <c r="H351" s="3" t="n"/>
-      <c r="I351" s="2" t="n"/>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>112004.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -12778,7 +12934,11 @@
         </is>
       </c>
       <c r="H352" s="3" t="n"/>
-      <c r="I352" s="2" t="n"/>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>112010.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -12809,7 +12969,11 @@
         </is>
       </c>
       <c r="H353" s="3" t="n"/>
-      <c r="I353" s="2" t="n"/>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>112011.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -12840,7 +13004,11 @@
         </is>
       </c>
       <c r="H354" s="3" t="n"/>
-      <c r="I354" s="2" t="n"/>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>111164.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -12871,7 +13039,11 @@
         </is>
       </c>
       <c r="H355" s="3" t="n"/>
-      <c r="I355" s="2" t="n"/>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>112528.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -12902,7 +13074,11 @@
         </is>
       </c>
       <c r="H356" s="3" t="n"/>
-      <c r="I356" s="2" t="n"/>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>112006.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -12933,7 +13109,11 @@
         </is>
       </c>
       <c r="H357" s="3" t="n"/>
-      <c r="I357" s="2" t="n"/>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>111188.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -12964,7 +13144,11 @@
         </is>
       </c>
       <c r="H358" s="3" t="n"/>
-      <c r="I358" s="2" t="n"/>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>111163.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -12995,7 +13179,11 @@
         </is>
       </c>
       <c r="H359" s="3" t="n"/>
-      <c r="I359" s="2" t="n"/>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>111179.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -13026,7 +13214,11 @@
         </is>
       </c>
       <c r="H360" s="3" t="n"/>
-      <c r="I360" s="2" t="n"/>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>113351.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -13162,7 +13354,11 @@
         </is>
       </c>
       <c r="H364" s="3" t="n"/>
-      <c r="I364" s="2" t="n"/>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>114332.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -13193,7 +13389,11 @@
         </is>
       </c>
       <c r="H365" s="3" t="n"/>
-      <c r="I365" s="2" t="n"/>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>111185.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -13224,7 +13424,11 @@
         </is>
       </c>
       <c r="H366" s="3" t="n"/>
-      <c r="I366" s="2" t="n"/>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>111185.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -13255,7 +13459,11 @@
         </is>
       </c>
       <c r="H367" s="3" t="n"/>
-      <c r="I367" s="2" t="n"/>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>112664.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -13321,7 +13529,11 @@
         </is>
       </c>
       <c r="H369" s="3" t="n"/>
-      <c r="I369" s="2" t="n"/>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>114258.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -13352,7 +13564,11 @@
         </is>
       </c>
       <c r="H370" s="3" t="n"/>
-      <c r="I370" s="2" t="n"/>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>113633.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -13383,7 +13599,11 @@
         </is>
       </c>
       <c r="H371" s="3" t="n"/>
-      <c r="I371" s="2" t="n"/>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>111163.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -13414,7 +13634,11 @@
         </is>
       </c>
       <c r="H372" s="3" t="n"/>
-      <c r="I372" s="2" t="n"/>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>114341.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -13445,7 +13669,11 @@
         </is>
       </c>
       <c r="H373" s="3" t="n"/>
-      <c r="I373" s="2" t="n"/>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>100433.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -13476,7 +13704,11 @@
         </is>
       </c>
       <c r="H374" s="3" t="n"/>
-      <c r="I374" s="2" t="n"/>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>100435.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -13507,7 +13739,11 @@
         </is>
       </c>
       <c r="H375" s="3" t="n"/>
-      <c r="I375" s="2" t="n"/>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>100436.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -13538,7 +13774,11 @@
         </is>
       </c>
       <c r="H376" s="3" t="n"/>
-      <c r="I376" s="2" t="n"/>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>100437.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -13569,7 +13809,11 @@
         </is>
       </c>
       <c r="H377" s="3" t="n"/>
-      <c r="I377" s="2" t="n"/>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>100438.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -13600,7 +13844,11 @@
         </is>
       </c>
       <c r="H378" s="3" t="n"/>
-      <c r="I378" s="2" t="n"/>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>111260.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -13631,7 +13879,11 @@
         </is>
       </c>
       <c r="H379" s="3" t="n"/>
-      <c r="I379" s="2" t="n"/>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>111263.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -13662,7 +13914,11 @@
         </is>
       </c>
       <c r="H380" s="3" t="n"/>
-      <c r="I380" s="2" t="n"/>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>100440.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -13693,7 +13949,11 @@
         </is>
       </c>
       <c r="H381" s="3" t="n"/>
-      <c r="I381" s="2" t="n"/>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>100442.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -13724,7 +13984,11 @@
         </is>
       </c>
       <c r="H382" s="3" t="n"/>
-      <c r="I382" s="2" t="n"/>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>100443.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -13755,7 +14019,11 @@
         </is>
       </c>
       <c r="H383" s="3" t="n"/>
-      <c r="I383" s="2" t="n"/>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>100445.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -13786,7 +14054,11 @@
         </is>
       </c>
       <c r="H384" s="3" t="n"/>
-      <c r="I384" s="2" t="n"/>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>111266.png</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -13817,7 +14089,11 @@
         </is>
       </c>
       <c r="H385" s="3" t="n"/>
-      <c r="I385" s="2" t="n"/>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>111267.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -13848,7 +14124,11 @@
         </is>
       </c>
       <c r="H386" s="3" t="n"/>
-      <c r="I386" s="2" t="n"/>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>111270.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -13879,7 +14159,11 @@
         </is>
       </c>
       <c r="H387" s="3" t="n"/>
-      <c r="I387" s="2" t="n"/>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>100421.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -13910,7 +14194,11 @@
         </is>
       </c>
       <c r="H388" s="3" t="n"/>
-      <c r="I388" s="2" t="n"/>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>100422.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n"/>
@@ -13937,7 +14225,11 @@
         </is>
       </c>
       <c r="H389" s="3" t="n"/>
-      <c r="I389" s="2" t="n"/>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>111221.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n"/>
@@ -13964,7 +14256,11 @@
         </is>
       </c>
       <c r="H390" s="3" t="n"/>
-      <c r="I390" s="2" t="n"/>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>111252.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n"/>
@@ -13991,7 +14287,11 @@
         </is>
       </c>
       <c r="H391" s="3" t="n"/>
-      <c r="I391" s="2" t="n"/>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>111253.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n"/>
@@ -14018,7 +14318,11 @@
         </is>
       </c>
       <c r="H392" s="3" t="n"/>
-      <c r="I392" s="2" t="n"/>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>111255.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n"/>
@@ -14045,7 +14349,11 @@
         </is>
       </c>
       <c r="H393" s="3" t="n"/>
-      <c r="I393" s="2" t="n"/>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>115250.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n"/>
@@ -14072,7 +14380,11 @@
         </is>
       </c>
       <c r="H394" s="3" t="n"/>
-      <c r="I394" s="2" t="n"/>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>115056.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -14103,7 +14415,11 @@
         </is>
       </c>
       <c r="H395" s="3" t="n"/>
-      <c r="I395" s="2" t="n"/>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>113382.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -14134,7 +14450,11 @@
         </is>
       </c>
       <c r="H396" s="3" t="n"/>
-      <c r="I396" s="2" t="n"/>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>114919.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -14165,7 +14485,11 @@
         </is>
       </c>
       <c r="H397" s="3" t="n"/>
-      <c r="I397" s="2" t="n"/>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>112555.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -14196,7 +14520,11 @@
         </is>
       </c>
       <c r="H398" s="3" t="n"/>
-      <c r="I398" s="2" t="n"/>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>111167.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -14227,7 +14555,11 @@
         </is>
       </c>
       <c r="H399" s="3" t="n"/>
-      <c r="I399" s="2" t="n"/>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>111264.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -14258,7 +14590,11 @@
         </is>
       </c>
       <c r="H400" s="3" t="n"/>
-      <c r="I400" s="2" t="n"/>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>111276.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -14289,7 +14625,11 @@
         </is>
       </c>
       <c r="H401" s="3" t="n"/>
-      <c r="I401" s="2" t="n"/>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>111243.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -14320,7 +14660,11 @@
         </is>
       </c>
       <c r="H402" s="3" t="n"/>
-      <c r="I402" s="2" t="n"/>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>115172.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -14351,7 +14695,11 @@
         </is>
       </c>
       <c r="H403" s="3" t="n"/>
-      <c r="I403" s="2" t="n"/>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>114956.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -14382,7 +14730,11 @@
         </is>
       </c>
       <c r="H404" s="3" t="n"/>
-      <c r="I404" s="2" t="n"/>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>114789.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -14448,7 +14800,11 @@
         </is>
       </c>
       <c r="H406" s="3" t="n"/>
-      <c r="I406" s="2" t="n"/>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>114353.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -14479,7 +14835,11 @@
         </is>
       </c>
       <c r="H407" s="3" t="n"/>
-      <c r="I407" s="2" t="n"/>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>114356.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -14510,7 +14870,11 @@
         </is>
       </c>
       <c r="H408" s="3" t="n"/>
-      <c r="I408" s="2" t="n"/>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>111964.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -14541,7 +14905,11 @@
         </is>
       </c>
       <c r="H409" s="3" t="n"/>
-      <c r="I409" s="2" t="n"/>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>111968.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -14572,7 +14940,11 @@
         </is>
       </c>
       <c r="H410" s="3" t="n"/>
-      <c r="I410" s="2" t="n"/>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>114480.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -14673,7 +15045,11 @@
         </is>
       </c>
       <c r="H413" s="3" t="n"/>
-      <c r="I413" s="2" t="n"/>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>112036.png</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -14774,7 +15150,11 @@
         </is>
       </c>
       <c r="H416" s="3" t="n"/>
-      <c r="I416" s="2" t="n"/>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>112357.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -14805,7 +15185,11 @@
         </is>
       </c>
       <c r="H417" s="3" t="n"/>
-      <c r="I417" s="2" t="n"/>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>112089.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -14836,7 +15220,11 @@
         </is>
       </c>
       <c r="H418" s="3" t="n"/>
-      <c r="I418" s="2" t="n"/>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>112035.png</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -14867,7 +15255,11 @@
         </is>
       </c>
       <c r="H419" s="3" t="n"/>
-      <c r="I419" s="2" t="n"/>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>112034.png</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -14898,7 +15290,11 @@
         </is>
       </c>
       <c r="H420" s="3" t="n"/>
-      <c r="I420" s="2" t="n"/>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>108556.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -14929,7 +15325,11 @@
         </is>
       </c>
       <c r="H421" s="3" t="n"/>
-      <c r="I421" s="2" t="n"/>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>113385.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -14960,7 +15360,11 @@
         </is>
       </c>
       <c r="H422" s="3" t="n"/>
-      <c r="I422" s="2" t="n"/>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>114927.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -14991,7 +15395,11 @@
         </is>
       </c>
       <c r="H423" s="3" t="n"/>
-      <c r="I423" s="2" t="n"/>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>111193.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -15127,7 +15535,11 @@
         </is>
       </c>
       <c r="H427" s="3" t="n"/>
-      <c r="I427" s="2" t="n"/>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>114465.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -15158,7 +15570,11 @@
         </is>
       </c>
       <c r="H428" s="3" t="n"/>
-      <c r="I428" s="2" t="n"/>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>115271.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -15329,7 +15745,11 @@
         </is>
       </c>
       <c r="H433" s="3" t="n"/>
-      <c r="I433" s="2" t="n"/>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>111192.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -15395,7 +15815,11 @@
         </is>
       </c>
       <c r="H435" s="3" t="n"/>
-      <c r="I435" s="2" t="n"/>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>100583.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -15426,7 +15850,11 @@
         </is>
       </c>
       <c r="H436" s="3" t="n"/>
-      <c r="I436" s="2" t="n"/>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>108362.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -15457,7 +15885,11 @@
         </is>
       </c>
       <c r="H437" s="3" t="n"/>
-      <c r="I437" s="2" t="n"/>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>115769.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -15488,7 +15920,11 @@
         </is>
       </c>
       <c r="H438" s="3" t="n"/>
-      <c r="I438" s="2" t="n"/>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>115769.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -15519,7 +15955,11 @@
         </is>
       </c>
       <c r="H439" s="3" t="n"/>
-      <c r="I439" s="2" t="n"/>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>108364.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -15550,7 +15990,11 @@
         </is>
       </c>
       <c r="H440" s="3" t="n"/>
-      <c r="I440" s="2" t="n"/>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>108365.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">

--- a/products.xlsx
+++ b/products.xlsx
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>106192.jpg</t>
+          <t>custom-sakaker-pistachio.jpg</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>100622.jpg</t>
+          <t>custom-sakaker-fruity.jpg</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>100623.jpg</t>
+          <t>custom-sakaker-caramel.jpg</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>114956.jpg</t>
+          <t>custom-dates-with-nuts-wrapped.jpg</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>101069.jpg</t>
+          <t>custom-colored-chocolate.jpg</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>101069.jpg</t>
+          <t>custom-spraied-chocolate.jpg</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>108627.jpg</t>
+          <t>custom-pastel-cone.jpg</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>101069.jpg</t>
+          <t>custom-painapple-chocolate.jpg</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,11 @@
       <c r="H103" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="I103" s="2" t="n"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>custom-bomigranant-chocoalte.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -4279,7 +4283,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>111574.jpg</t>
+          <t>custom-red-burry-chocolate.jpg</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4318,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>101069.jpg</t>
+          <t>custom-blackburry-chocolate.jpg</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4388,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>101069.jpg</t>
+          <t>custom-shell-chocolate.jpg</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -4285,7 +4285,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>101069.jpg</t>
+          <t>custom-tear-chocolate.jpg</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>110480.jpg</t>
+          <t>custom-kunafa-pistachio-bar-190g.jpg</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,11 @@
       <c r="H122" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="I122" s="15" t="n"/>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>custom-ain-aljamal-mix.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="123" customFormat="1" s="18">
       <c r="A123" s="15" t="inlineStr">
@@ -5123,7 +5127,11 @@
       <c r="H128" s="17" t="n">
         <v>110</v>
       </c>
-      <c r="I128" s="15" t="n"/>
+      <c r="I128" s="15" t="inlineStr">
+        <is>
+          <t>custom-salted-biscuit-mix.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="129" customFormat="1" s="18">
       <c r="A129" s="15" t="n">
@@ -5401,7 +5409,7 @@
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>112516.jpg</t>
+          <t>custom-premium-mille-feuille-mix.jpg</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5656,7 @@
       </c>
       <c r="I143" s="15" t="inlineStr">
         <is>
-          <t>112596.jpg</t>
+          <t>custom-premium-salted-stick-mix.jpg</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7282,7 @@
       </c>
       <c r="I189" s="15" t="inlineStr">
         <is>
-          <t>112024.jpg</t>
+          <t>custom-premium-truffles-mix.jpg</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13192,11 @@
       <c r="H351" s="17" t="n">
         <v>147</v>
       </c>
-      <c r="I351" s="15" t="n"/>
+      <c r="I351" s="15" t="inlineStr">
+        <is>
+          <t>custom-dates-mix-sagai.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="352" customFormat="1" s="18">
       <c r="A352" s="15" t="inlineStr">
@@ -13809,7 +13821,11 @@
       <c r="H368" s="17" t="n">
         <v>147</v>
       </c>
-      <c r="I368" s="15" t="n"/>
+      <c r="I368" s="15" t="inlineStr">
+        <is>
+          <t>custom-apricot-with-nuts-mix.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="369" customFormat="1" s="18">
       <c r="A369" s="15" t="inlineStr">
@@ -16503,7 +16519,11 @@
       <c r="H444" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="I444" s="2" t="n"/>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>custom-majdool-dates-with-nuts.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">

--- a/products.xlsx
+++ b/products.xlsx
@@ -6024,7 +6024,11 @@
       <c r="H153" s="3" t="n">
         <v>136.5</v>
       </c>
-      <c r="I153" s="2" t="n"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>112393.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6057,7 +6061,11 @@
       <c r="H154" s="3" t="n">
         <v>141.75</v>
       </c>
-      <c r="I154" s="2" t="n"/>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>100318.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">

--- a/products.xlsx
+++ b/products.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$I$468</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Products'!$A$1:$I$462</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I567"/>
+  <dimension ref="A1:I561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="D350" s="15" t="inlineStr">
         <is>
-          <t>Secondary items</t>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E350" s="15" t="n"/>
@@ -14221,9 +14221,9 @@
           <t>Dates</t>
         </is>
       </c>
-      <c r="D379" s="2" t="inlineStr">
-        <is>
-          <t>Secondary items</t>
+      <c r="D379" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E379" s="2" t="n"/>
@@ -14467,17 +14467,17 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>100247</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Premium ain jamal zafran kg</t>
+          <t>Premium baklawa wrapped pecan walnut kg</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Ain jamal</t>
+          <t>Baklawa</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -14495,24 +14495,24 @@
       <c r="H386" s="3" t="n"/>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>112036.png</t>
+          <t>113385.jpg</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>100250</t>
+          <t>115402</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Premium ain jamal red velvet kg</t>
+          <t>Premium baklawa wrapped square lotus with pistachio kgs</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>Ain jamal</t>
+          <t>Baklawa</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -14530,24 +14530,24 @@
       <c r="H387" s="3" t="n"/>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>112357.jpg</t>
+          <t>114927.jpg</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>100251</t>
-        </is>
-      </c>
-      <c r="B388" s="2" t="inlineStr">
-        <is>
-          <t>Premium ain jamal lotus kg</t>
+          <t>100303</t>
+        </is>
+      </c>
+      <c r="B388" s="11" t="inlineStr">
+        <is>
+          <t>Premium italian wrapped baklawa kg</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Ain jamal</t>
+          <t>Baklawa</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -14565,99 +14565,99 @@
       <c r="H388" s="3" t="n"/>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>112089.jpg</t>
+          <t>111193.jpg</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>100252</t>
-        </is>
-      </c>
-      <c r="B389" s="2" t="inlineStr">
-        <is>
-          <t>Premium ain jamal nuttela kg</t>
+          <t>100060</t>
+        </is>
+      </c>
+      <c r="B389" s="16" t="inlineStr">
+        <is>
+          <t>Premium mixed baklawa 400g- pcs</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>Ain jamal</t>
+          <t>Baklawa</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Secondary items</t>
+          <t>Arabic sweets</t>
         </is>
       </c>
       <c r="E389" s="2" t="n"/>
       <c r="F389" s="2" t="n"/>
-      <c r="G389" s="15" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H389" s="3" t="n"/>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>112035.png</t>
+          <t>100060.jpg</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>100253</t>
-        </is>
-      </c>
-      <c r="B390" s="2" t="inlineStr">
-        <is>
-          <t>Premium ain jamal caramel kg</t>
+          <t>100061</t>
+        </is>
+      </c>
+      <c r="B390" s="16" t="inlineStr">
+        <is>
+          <t>Premium mixed baklawa 740g- pcs (100)</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Ain jamal</t>
+          <t>Baklawa</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Secondary items</t>
+          <t>Arabic sweets</t>
         </is>
       </c>
       <c r="E390" s="2" t="n"/>
       <c r="F390" s="2" t="n"/>
-      <c r="G390" s="15" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H390" s="3" t="n"/>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>112034.png</t>
+          <t>100061.jpeg</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>100254</t>
-        </is>
-      </c>
-      <c r="B391" s="2" t="inlineStr">
-        <is>
-          <t>Premium ain al jamal brown kg</t>
+          <t>100059</t>
+        </is>
+      </c>
+      <c r="B391" s="16" t="inlineStr">
+        <is>
+          <t>Premium mixed baklawa 1000g (2523)</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>Ain jamal</t>
+          <t>Baklawa</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Secondary items</t>
+          <t>Arabic sweets</t>
         </is>
       </c>
       <c r="E391" s="2" t="n"/>
@@ -14670,19 +14670,19 @@
       <c r="H391" s="3" t="n"/>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>108556.jpg</t>
+          <t>100059.jpg</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>113885</t>
-        </is>
-      </c>
-      <c r="B392" s="2" t="inlineStr">
-        <is>
-          <t>Premium baklawa wrapped pecan walnut kg</t>
+          <t>115402</t>
+        </is>
+      </c>
+      <c r="B392" s="11" t="inlineStr">
+        <is>
+          <t>Premium baklawa open nougat square mix nuts kg</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -14705,7 +14705,7 @@
       <c r="H392" s="3" t="n"/>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>113385.jpg</t>
+          <t>114465.jpg</t>
         </is>
       </c>
     </row>
@@ -14715,9 +14715,9 @@
           <t>115402</t>
         </is>
       </c>
-      <c r="B393" s="2" t="inlineStr">
-        <is>
-          <t>Premium baklawa wrapped square lotus with pistachio kgs</t>
+      <c r="B393" s="11" t="inlineStr">
+        <is>
+          <t>Premium baklawa wrapped almond cream with white walnut kg</t>
         </is>
       </c>
       <c r="C393" s="2" t="inlineStr">
@@ -14740,64 +14740,64 @@
       <c r="H393" s="3" t="n"/>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>114927.jpg</t>
+          <t>115271.jpg</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>100303</t>
+          <t>113519</t>
         </is>
       </c>
       <c r="B394" s="11" t="inlineStr">
         <is>
-          <t>Premium italian wrapped baklawa kg</t>
+          <t>Arabic coffee 450g pkt (112853)</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Baklawa</t>
+          <t>Arabic coffee</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Secondary items</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="E394" s="2" t="n"/>
       <c r="F394" s="2" t="n"/>
-      <c r="G394" s="15" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H394" s="3" t="n"/>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>111193.jpg</t>
+          <t>113519.jpg</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>100060</t>
-        </is>
-      </c>
-      <c r="B395" s="16" t="inlineStr">
-        <is>
-          <t>Premium mixed baklawa 400g- pcs</t>
+          <t>113518</t>
+        </is>
+      </c>
+      <c r="B395" s="11" t="inlineStr">
+        <is>
+          <t>Arabic coffee 900g pkt (112852)</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>Baklawa</t>
+          <t>Arabic coffee</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Arabic sweets</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="E395" s="2" t="n"/>
@@ -14810,29 +14810,29 @@
       <c r="H395" s="3" t="n"/>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>100060.jpg</t>
+          <t>113518.jpg</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>100061</t>
-        </is>
-      </c>
-      <c r="B396" s="16" t="inlineStr">
-        <is>
-          <t>Premium mixed baklawa 740g- pcs (100)</t>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="B396" s="11" t="inlineStr">
+        <is>
+          <t>Arabic coffee 450 gm jar- pc</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Baklawa</t>
+          <t>Arabic coffee</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Arabic sweets</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="E396" s="2" t="n"/>
@@ -14845,64 +14845,64 @@
       <c r="H396" s="3" t="n"/>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>100061.jpeg</t>
+          <t>100000.JPG</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>100059</t>
-        </is>
-      </c>
-      <c r="B397" s="16" t="inlineStr">
-        <is>
-          <t>Premium mixed baklawa 1000g (2523)</t>
+          <t>100003</t>
+        </is>
+      </c>
+      <c r="B397" s="11" t="inlineStr">
+        <is>
+          <t>Arabic coffee 500g- pcs</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>Baklawa</t>
+          <t>Arabic coffee</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Arabic sweets</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="E397" s="2" t="n"/>
       <c r="F397" s="2" t="n"/>
-      <c r="G397" s="15" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H397" s="3" t="n"/>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>100059.jpg</t>
+          <t>100003.png</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>115402</t>
+          <t>100303</t>
         </is>
       </c>
       <c r="B398" s="11" t="inlineStr">
         <is>
-          <t>Premium baklawa open nougat square mix nuts kg</t>
-        </is>
-      </c>
-      <c r="C398" s="2" t="inlineStr">
-        <is>
-          <t>Baklawa</t>
-        </is>
-      </c>
-      <c r="D398" s="2" t="inlineStr">
-        <is>
-          <t>Secondary items</t>
+          <t>Premium italian wrapped coffee latte kg</t>
+        </is>
+      </c>
+      <c r="C398" s="10" t="inlineStr">
+        <is>
+          <t>Normal italian</t>
+        </is>
+      </c>
+      <c r="D398" s="10" t="inlineStr">
+        <is>
+          <t>Italian Chocolate</t>
         </is>
       </c>
       <c r="E398" s="2" t="n"/>
@@ -14915,234 +14915,234 @@
       <c r="H398" s="3" t="n"/>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>114465.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="2" t="inlineStr">
-        <is>
-          <t>115402</t>
-        </is>
-      </c>
-      <c r="B399" s="11" t="inlineStr">
-        <is>
-          <t>Premium baklawa wrapped almond cream with white walnut kg</t>
-        </is>
-      </c>
-      <c r="C399" s="2" t="inlineStr">
-        <is>
-          <t>Baklawa</t>
-        </is>
-      </c>
-      <c r="D399" s="2" t="inlineStr">
-        <is>
-          <t>Secondary items</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="n"/>
-      <c r="F399" s="2" t="n"/>
+          <t>111192.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" customFormat="1" s="18">
+      <c r="A399" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100571 </t>
+        </is>
+      </c>
+      <c r="B399" s="16" t="inlineStr">
+        <is>
+          <t>Premium coconut mist 500g jar- pcs</t>
+        </is>
+      </c>
+      <c r="C399" s="15" t="inlineStr">
+        <is>
+          <t>Coconut</t>
+        </is>
+      </c>
+      <c r="D399" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E399" s="15" t="n"/>
+      <c r="F399" s="15" t="n"/>
       <c r="G399" s="15" t="inlineStr">
         <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H399" s="3" t="n"/>
-      <c r="I399" s="2" t="inlineStr">
-        <is>
-          <t>115271.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="2" t="inlineStr">
-        <is>
-          <t>113519</t>
-        </is>
-      </c>
-      <c r="B400" s="11" t="inlineStr">
-        <is>
-          <t>Arabic coffee 450g pkt (112853)</t>
-        </is>
-      </c>
-      <c r="C400" s="2" t="inlineStr">
-        <is>
-          <t>Arabic coffee</t>
-        </is>
-      </c>
-      <c r="D400" s="2" t="inlineStr">
-        <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="E400" s="2" t="n"/>
-      <c r="F400" s="2" t="n"/>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H400" s="3" t="n"/>
-      <c r="I400" s="2" t="inlineStr">
-        <is>
-          <t>113519.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="2" t="inlineStr">
-        <is>
-          <t>113518</t>
-        </is>
-      </c>
-      <c r="B401" s="11" t="inlineStr">
-        <is>
-          <t>Arabic coffee 900g pkt (112852)</t>
-        </is>
-      </c>
-      <c r="C401" s="2" t="inlineStr">
-        <is>
-          <t>Arabic coffee</t>
-        </is>
-      </c>
-      <c r="D401" s="2" t="inlineStr">
-        <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="E401" s="2" t="n"/>
-      <c r="F401" s="2" t="n"/>
-      <c r="G401" s="2" t="inlineStr">
+      <c r="H399" s="17" t="n"/>
+      <c r="I399" s="15" t="inlineStr">
+        <is>
+          <t>100571.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" customFormat="1" s="18">
+      <c r="A400" s="15" t="inlineStr">
+        <is>
+          <t>100492</t>
+        </is>
+      </c>
+      <c r="B400" s="16" t="inlineStr">
+        <is>
+          <t>Premium petit four truffles cacao 500g jar- pcs</t>
+        </is>
+      </c>
+      <c r="C400" s="15" t="inlineStr">
+        <is>
+          <t>Truffles</t>
+        </is>
+      </c>
+      <c r="D400" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E400" s="15" t="n"/>
+      <c r="F400" s="15" t="n"/>
+      <c r="G400" s="15" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H401" s="3" t="n"/>
-      <c r="I401" s="2" t="inlineStr">
-        <is>
-          <t>113518.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="2" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="B402" s="11" t="inlineStr">
-        <is>
-          <t>Arabic coffee 450 gm jar- pc</t>
-        </is>
-      </c>
-      <c r="C402" s="2" t="inlineStr">
-        <is>
-          <t>Arabic coffee</t>
-        </is>
-      </c>
-      <c r="D402" s="2" t="inlineStr">
-        <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="E402" s="2" t="n"/>
-      <c r="F402" s="2" t="n"/>
-      <c r="G402" s="2" t="inlineStr">
+      <c r="H400" s="17" t="n"/>
+      <c r="I400" s="15" t="inlineStr">
+        <is>
+          <t>100583.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" customFormat="1" s="18">
+      <c r="A401" s="15" t="inlineStr">
+        <is>
+          <t>100492</t>
+        </is>
+      </c>
+      <c r="B401" s="16" t="inlineStr">
+        <is>
+          <t>Premium truffles caramel 500g jar- pcs</t>
+        </is>
+      </c>
+      <c r="C401" s="15" t="inlineStr">
+        <is>
+          <t>Truffles</t>
+        </is>
+      </c>
+      <c r="D401" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E401" s="15" t="n"/>
+      <c r="F401" s="15" t="n"/>
+      <c r="G401" s="15" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H402" s="3" t="n"/>
-      <c r="I402" s="2" t="inlineStr">
-        <is>
-          <t>100000.JPG</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" s="2" t="inlineStr">
-        <is>
-          <t>100003</t>
-        </is>
-      </c>
-      <c r="B403" s="11" t="inlineStr">
-        <is>
-          <t>Arabic coffee 500g- pcs</t>
-        </is>
-      </c>
-      <c r="C403" s="2" t="inlineStr">
-        <is>
-          <t>Arabic coffee</t>
-        </is>
-      </c>
-      <c r="D403" s="2" t="inlineStr">
-        <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="E403" s="2" t="n"/>
-      <c r="F403" s="2" t="n"/>
-      <c r="G403" s="2" t="inlineStr">
+      <c r="H401" s="17" t="n"/>
+      <c r="I401" s="15" t="inlineStr">
+        <is>
+          <t>108362.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" customFormat="1" s="18">
+      <c r="A402" s="15" t="inlineStr">
+        <is>
+          <t>100492</t>
+        </is>
+      </c>
+      <c r="B402" s="16" t="inlineStr">
+        <is>
+          <t>Premium truffles hazelnut cream 500g jar- pcs</t>
+        </is>
+      </c>
+      <c r="C402" s="15" t="inlineStr">
+        <is>
+          <t>Truffles</t>
+        </is>
+      </c>
+      <c r="D402" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E402" s="15" t="n"/>
+      <c r="F402" s="15" t="n"/>
+      <c r="G402" s="15" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H403" s="3" t="n"/>
-      <c r="I403" s="2" t="inlineStr">
-        <is>
-          <t>100003.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="2" t="inlineStr">
-        <is>
-          <t>100303</t>
-        </is>
-      </c>
-      <c r="B404" s="11" t="inlineStr">
-        <is>
-          <t>Premium italian wrapped coffee latte kg</t>
-        </is>
-      </c>
-      <c r="C404" s="10" t="inlineStr">
-        <is>
-          <t>Normal italian</t>
-        </is>
-      </c>
-      <c r="D404" s="10" t="inlineStr">
-        <is>
-          <t>Italian Chocolate</t>
-        </is>
-      </c>
-      <c r="E404" s="2" t="n"/>
-      <c r="F404" s="2" t="n"/>
+      <c r="H402" s="17" t="n"/>
+      <c r="I402" s="15" t="inlineStr">
+        <is>
+          <t>115769.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" customFormat="1" s="18">
+      <c r="A403" s="15" t="inlineStr">
+        <is>
+          <t>100492</t>
+        </is>
+      </c>
+      <c r="B403" s="16" t="inlineStr">
+        <is>
+          <t>Premium truffles nutella dark 500g jar- pcs</t>
+        </is>
+      </c>
+      <c r="C403" s="15" t="inlineStr">
+        <is>
+          <t>Truffles</t>
+        </is>
+      </c>
+      <c r="D403" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E403" s="15" t="n"/>
+      <c r="F403" s="15" t="n"/>
+      <c r="G403" s="15" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="H403" s="17" t="n"/>
+      <c r="I403" s="15" t="inlineStr">
+        <is>
+          <t>108364.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" customFormat="1" s="18">
+      <c r="A404" s="15" t="inlineStr">
+        <is>
+          <t>100492</t>
+        </is>
+      </c>
+      <c r="B404" s="16" t="inlineStr">
+        <is>
+          <t>Premium truffles pomegranate 500g jar- pcs</t>
+        </is>
+      </c>
+      <c r="C404" s="15" t="inlineStr">
+        <is>
+          <t>Truffles</t>
+        </is>
+      </c>
+      <c r="D404" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
+        </is>
+      </c>
+      <c r="E404" s="15" t="n"/>
+      <c r="F404" s="15" t="n"/>
       <c r="G404" s="15" t="inlineStr">
         <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H404" s="3" t="n"/>
-      <c r="I404" s="2" t="inlineStr">
-        <is>
-          <t>111192.jpg</t>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="H404" s="17" t="n"/>
+      <c r="I404" s="15" t="inlineStr">
+        <is>
+          <t>108365.jpg</t>
         </is>
       </c>
     </row>
     <row r="405" customFormat="1" s="18">
       <c r="A405" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">100571 </t>
+          <t xml:space="preserve">108975 </t>
         </is>
       </c>
       <c r="B405" s="16" t="inlineStr">
         <is>
-          <t>Premium coconut mist 500g jar- pcs</t>
+          <t>Truffles honey 500g jar- pcs</t>
         </is>
       </c>
       <c r="C405" s="15" t="inlineStr">
         <is>
-          <t>Coconut</t>
+          <t>Truffles</t>
         </is>
       </c>
       <c r="D405" s="15" t="inlineStr">
@@ -15160,19 +15160,19 @@
       <c r="H405" s="17" t="n"/>
       <c r="I405" s="15" t="inlineStr">
         <is>
-          <t>100571.jpg</t>
+          <t>108975.jpg</t>
         </is>
       </c>
     </row>
     <row r="406" customFormat="1" s="18">
       <c r="A406" s="15" t="inlineStr">
         <is>
-          <t>100492</t>
+          <t xml:space="preserve">108976 </t>
         </is>
       </c>
       <c r="B406" s="16" t="inlineStr">
         <is>
-          <t>Premium petit four truffles cacao 500g jar- pcs</t>
+          <t>Truffles mango 500g jar- pcs</t>
         </is>
       </c>
       <c r="C406" s="15" t="inlineStr">
@@ -15195,19 +15195,19 @@
       <c r="H406" s="17" t="n"/>
       <c r="I406" s="15" t="inlineStr">
         <is>
-          <t>100583.jpg</t>
+          <t>108976.jpg</t>
         </is>
       </c>
     </row>
     <row r="407" customFormat="1" s="18">
       <c r="A407" s="15" t="inlineStr">
         <is>
-          <t>100492</t>
+          <t xml:space="preserve">108406 </t>
         </is>
       </c>
       <c r="B407" s="16" t="inlineStr">
         <is>
-          <t>Premium truffles caramel 500g jar- pcs</t>
+          <t>Truffles pistachio 500g jar- pcs</t>
         </is>
       </c>
       <c r="C407" s="15" t="inlineStr">
@@ -15230,239 +15230,241 @@
       <c r="H407" s="17" t="n"/>
       <c r="I407" s="15" t="inlineStr">
         <is>
-          <t>108362.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="408" customFormat="1" s="18">
-      <c r="A408" s="15" t="inlineStr">
-        <is>
-          <t>100492</t>
-        </is>
-      </c>
-      <c r="B408" s="16" t="inlineStr">
-        <is>
-          <t>Premium truffles hazelnut cream 500g jar- pcs</t>
-        </is>
-      </c>
-      <c r="C408" s="15" t="inlineStr">
-        <is>
-          <t>Truffles</t>
-        </is>
-      </c>
-      <c r="D408" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="E408" s="15" t="n"/>
-      <c r="F408" s="15" t="n"/>
-      <c r="G408" s="15" t="inlineStr">
+          <t>108406.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>100230</t>
+        </is>
+      </c>
+      <c r="B408" s="11" t="inlineStr">
+        <is>
+          <t>Happy ball open pistachio chocolate pc</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Secondary items</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n"/>
+      <c r="F408" s="2" t="n"/>
+      <c r="G408" s="2" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H408" s="17" t="n"/>
-      <c r="I408" s="15" t="inlineStr">
-        <is>
-          <t>115769.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="409" customFormat="1" s="18">
-      <c r="A409" s="15" t="inlineStr">
-        <is>
-          <t>100492</t>
-        </is>
-      </c>
-      <c r="B409" s="16" t="inlineStr">
-        <is>
-          <t>Premium truffles nutella dark 500g jar- pcs</t>
-        </is>
-      </c>
-      <c r="C409" s="15" t="inlineStr">
-        <is>
-          <t>Truffles</t>
-        </is>
-      </c>
-      <c r="D409" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="E409" s="15" t="n"/>
-      <c r="F409" s="15" t="n"/>
-      <c r="G409" s="15" t="inlineStr">
+      <c r="H408" s="3" t="n"/>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>100230.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106393 </t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>Ab Vacuum Flask 0.6 + 1.0lt (S203)</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n"/>
+      <c r="F409" s="2" t="n"/>
+      <c r="G409" s="2" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H409" s="17" t="n"/>
-      <c r="I409" s="15" t="inlineStr">
-        <is>
-          <t>108364.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="410" customFormat="1" s="18">
-      <c r="A410" s="15" t="inlineStr">
-        <is>
-          <t>100492</t>
-        </is>
-      </c>
-      <c r="B410" s="16" t="inlineStr">
-        <is>
-          <t>Premium truffles pomegranate 500g jar- pcs</t>
-        </is>
-      </c>
-      <c r="C410" s="15" t="inlineStr">
-        <is>
-          <t>Truffles</t>
-        </is>
-      </c>
-      <c r="D410" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="E410" s="15" t="n"/>
-      <c r="F410" s="15" t="n"/>
-      <c r="G410" s="15" t="inlineStr">
+      <c r="H409" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>custom-ab-vacuum-flask-0-6-1-0lt-s203.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102171 </t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Thermall Roll</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>Stationery</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n"/>
+      <c r="F410" s="2" t="n"/>
+      <c r="G410" s="2" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H410" s="17" t="n"/>
-      <c r="I410" s="15" t="inlineStr">
-        <is>
-          <t>108365.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="411" customFormat="1" s="18">
-      <c r="A411" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108975 </t>
-        </is>
-      </c>
-      <c r="B411" s="16" t="inlineStr">
-        <is>
-          <t>Truffles honey 500g jar- pcs</t>
-        </is>
-      </c>
-      <c r="C411" s="15" t="inlineStr">
-        <is>
-          <t>Truffles</t>
-        </is>
-      </c>
-      <c r="D411" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="E411" s="15" t="n"/>
-      <c r="F411" s="15" t="n"/>
-      <c r="G411" s="15" t="inlineStr">
+      <c r="H410" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>custom-thermall-roll.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>105349</v>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>Foam cone h30 x dia 15 empty</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>Styro</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Decoration</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n"/>
+      <c r="F411" s="2" t="n"/>
+      <c r="G411" s="2" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H411" s="17" t="n"/>
-      <c r="I411" s="15" t="inlineStr">
-        <is>
-          <t>108975.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="412" customFormat="1" s="18">
-      <c r="A412" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108976 </t>
-        </is>
-      </c>
-      <c r="B412" s="16" t="inlineStr">
-        <is>
-          <t>Truffles mango 500g jar- pcs</t>
-        </is>
-      </c>
-      <c r="C412" s="15" t="inlineStr">
-        <is>
-          <t>Truffles</t>
-        </is>
-      </c>
-      <c r="D412" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="E412" s="15" t="n"/>
-      <c r="F412" s="15" t="n"/>
-      <c r="G412" s="15" t="inlineStr">
+      <c r="H411" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>105349.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>105350</v>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Foam cone h40 x dia 20 empty</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>Styro</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Decoration</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="n"/>
+      <c r="F412" s="2" t="n"/>
+      <c r="G412" s="2" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H412" s="17" t="n"/>
-      <c r="I412" s="15" t="inlineStr">
-        <is>
-          <t>108976.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="413" customFormat="1" s="18">
-      <c r="A413" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108406 </t>
-        </is>
-      </c>
-      <c r="B413" s="16" t="inlineStr">
-        <is>
-          <t>Truffles pistachio 500g jar- pcs</t>
-        </is>
-      </c>
-      <c r="C413" s="15" t="inlineStr">
-        <is>
-          <t>Truffles</t>
-        </is>
-      </c>
-      <c r="D413" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="E413" s="15" t="n"/>
-      <c r="F413" s="15" t="n"/>
-      <c r="G413" s="15" t="inlineStr">
+      <c r="H412" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>105350.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>105351</v>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>Foam cone h40 x dia 25 empty</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>Styro</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Decoration</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="n"/>
+      <c r="F413" s="2" t="n"/>
+      <c r="G413" s="2" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="H413" s="17" t="n"/>
-      <c r="I413" s="15" t="inlineStr">
-        <is>
-          <t>108406.jpg</t>
+      <c r="H413" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>105351.png</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="inlineStr">
-        <is>
-          <t>100230</t>
-        </is>
-      </c>
-      <c r="B414" s="11" t="inlineStr">
-        <is>
-          <t>Happy ball open pistachio chocolate pc</t>
+      <c r="A414" s="2" t="n">
+        <v>105352</v>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>Foam cone h60 x dia 30 empty</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Special</t>
+          <t>Styro</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Secondary items</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="E414" s="2" t="n"/>
@@ -15472,32 +15474,32 @@
           <t>PCS</t>
         </is>
       </c>
-      <c r="H414" s="3" t="n"/>
+      <c r="H414" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>100230.jpg</t>
+          <t>105352.jpg</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106393 </t>
-        </is>
+      <c r="A415" s="2" t="n">
+        <v>105622</v>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Ab Vacuum Flask 0.6 + 1.0lt (S203)</t>
+          <t>Foam cone height 100cm x dia 40cm</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Styro</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="E415" s="2" t="n"/>
@@ -15512,29 +15514,27 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>custom-ab-vacuum-flask-0-6-1-0lt-s203.jpg</t>
+          <t>105622.png</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102171 </t>
-        </is>
+      <c r="A416" s="2" t="n">
+        <v>105355</v>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Thermall Roll</t>
+          <t>Foam pillar round 10h x 10 dia empty</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Styro</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="E416" s="2" t="n"/>
@@ -15549,17 +15549,17 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>custom-thermall-roll.jpg</t>
+          <t>105355.jpg</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
-        <v>105349</v>
+        <v>105369</v>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Foam cone h30 x dia 15 empty</t>
+          <t>Foam pillar round h-15cm x dia 15cm</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
@@ -15584,17 +15584,17 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>105349.png</t>
+          <t>105369.jpg</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
-        <v>105350</v>
+        <v>105370</v>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>Foam cone h40 x dia 20 empty</t>
+          <t>Foam pillar round h-15cm x dia 20cm</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
@@ -15619,17 +15619,17 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>105350.jpg</t>
+          <t>105370.jpg</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
-        <v>105351</v>
+        <v>105371</v>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>Foam cone h40 x dia 25 empty</t>
+          <t>Foam pillar round h-15cm x dia 25cm</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
@@ -15654,22 +15654,22 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>105351.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
+          <t>105371.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="2" t="n">
-        <v>105352</v>
-      </c>
-      <c r="B420" s="2" t="inlineStr">
-        <is>
-          <t>Foam cone h60 x dia 30 empty</t>
+        <v>103218</v>
+      </c>
+      <c r="B420" s="20" t="inlineStr">
+        <is>
+          <t>Bio deg pe clear gloves</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Styro</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -15689,22 +15689,22 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>105352.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
+          <t>103218.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="2" t="n">
-        <v>105622</v>
-      </c>
-      <c r="B421" s="2" t="inlineStr">
-        <is>
-          <t>Foam cone height 100cm x dia 40cm</t>
+        <v>103234</v>
+      </c>
+      <c r="B421" s="20" t="inlineStr">
+        <is>
+          <t>Garbage bag ( decoration store)</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>Styro</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
@@ -15724,22 +15724,22 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>105622.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
+          <t>103234.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="2" t="n">
-        <v>105355</v>
-      </c>
-      <c r="B422" s="2" t="inlineStr">
-        <is>
-          <t>Foam pillar round 10h x 10 dia empty</t>
+        <v>103233</v>
+      </c>
+      <c r="B422" s="20" t="inlineStr">
+        <is>
+          <t>Garbage bag</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Styro</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -15759,22 +15759,22 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>105355.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
+          <t>103233.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="2" t="n">
-        <v>105369</v>
-      </c>
-      <c r="B423" s="2" t="inlineStr">
-        <is>
-          <t>Foam pillar round h-15cm x dia 15cm</t>
+        <v>103240</v>
+      </c>
+      <c r="B423" s="20" t="inlineStr">
+        <is>
+          <t>Nonwowen bouffant cap 21"" - (p:1000pcs)"</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>Styro</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -15786,7 +15786,7 @@
       <c r="F423" s="2" t="n"/>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>CARTON</t>
         </is>
       </c>
       <c r="H423" s="3" t="n">
@@ -15794,22 +15794,22 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>105369.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
+          <t>103240.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="2" t="n">
-        <v>105370</v>
-      </c>
-      <c r="B424" s="2" t="inlineStr">
-        <is>
-          <t>Foam pillar round h-15cm x dia 20cm</t>
+        <v>102282</v>
+      </c>
+      <c r="B424" s="20" t="inlineStr">
+        <is>
+          <t>Plastic cup white 6oz</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Styro</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -15821,7 +15821,7 @@
       <c r="F424" s="2" t="n"/>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>CARTON</t>
         </is>
       </c>
       <c r="H424" s="3" t="n">
@@ -15829,22 +15829,22 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>105370.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
+          <t>102282.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="2" t="n">
-        <v>105371</v>
-      </c>
-      <c r="B425" s="2" t="inlineStr">
-        <is>
-          <t>Foam pillar round h-15cm x dia 25cm</t>
+        <v>102285</v>
+      </c>
+      <c r="B425" s="20" t="inlineStr">
+        <is>
+          <t>Printed coffee cup 6oz (20*50's)</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>Styro</t>
+          <t>Disposable</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -15856,7 +15856,7 @@
       <c r="F425" s="2" t="n"/>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>CARTON</t>
         </is>
       </c>
       <c r="H425" s="3" t="n">
@@ -15864,22 +15864,22 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>105371.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="426" ht="15.75" customHeight="1">
+          <t>102285.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
       <c r="A426" s="2" t="n">
-        <v>103218</v>
-      </c>
-      <c r="B426" s="20" t="inlineStr">
-        <is>
-          <t>Bio deg pe clear gloves</t>
+        <v>103072</v>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>Bag chocolala 19*19*19cm</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Disposable</t>
+          <t>Bags</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -15891,7 +15891,7 @@
       <c r="F426" s="2" t="n"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>CARTON</t>
         </is>
       </c>
       <c r="H426" s="3" t="n">
@@ -15899,22 +15899,22 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>103218.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="427" ht="15.75" customHeight="1">
+          <t>103072.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
       <c r="A427" s="2" t="n">
-        <v>103234</v>
-      </c>
-      <c r="B427" s="20" t="inlineStr">
-        <is>
-          <t>Garbage bag ( decoration store)</t>
+        <v>103073</v>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Bag chocolala 29*12*15cm (1kg) (1007-3)</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>Disposable</t>
+          <t>Bags</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
@@ -15926,7 +15926,7 @@
       <c r="F427" s="2" t="n"/>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>CARTON</t>
         </is>
       </c>
       <c r="H427" s="3" t="n">
@@ -15934,22 +15934,22 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>103234.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="428" ht="15.75" customHeight="1">
+          <t>103073.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
       <c r="A428" s="2" t="n">
-        <v>103233</v>
-      </c>
-      <c r="B428" s="20" t="inlineStr">
-        <is>
-          <t>Garbage bag</t>
+        <v>103074</v>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>Bag chocolala 29*29*29cm</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Disposable</t>
+          <t>Bags</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -15961,7 +15961,7 @@
       <c r="F428" s="2" t="n"/>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>CARTON</t>
         </is>
       </c>
       <c r="H428" s="3" t="n">
@@ -15969,22 +15969,22 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>103233.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="429" ht="15.75" customHeight="1">
+          <t>103074.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
       <c r="A429" s="2" t="n">
-        <v>103240</v>
-      </c>
-      <c r="B429" s="20" t="inlineStr">
-        <is>
-          <t>Nonwowen bouffant cap 21"" - (p:1000pcs)"</t>
+        <v>103075</v>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>Bag chocolala 34*34*34cm</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>Disposable</t>
+          <t>Bags</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
@@ -16004,22 +16004,22 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>103240.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="430" ht="15.75" customHeight="1">
+          <t>103075.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
       <c r="A430" s="2" t="n">
-        <v>102282</v>
-      </c>
-      <c r="B430" s="20" t="inlineStr">
-        <is>
-          <t>Plastic cup white 6oz</t>
+        <v>103076</v>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>Bag chocolala 50*40*40cm</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Disposable</t>
+          <t>Bags</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
@@ -16039,22 +16039,22 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>102282.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="431" ht="15.75" customHeight="1">
+          <t>103076.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
       <c r="A431" s="2" t="n">
-        <v>102285</v>
-      </c>
-      <c r="B431" s="20" t="inlineStr">
-        <is>
-          <t>Printed coffee cup 6oz (20*50's)</t>
+        <v>103077</v>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Bag chocolala 57*36*40cm</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>Disposable</t>
+          <t>Bags</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
@@ -16074,17 +16074,17 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>102285.jpg</t>
+          <t>103077.jpg</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
-        <v>103072</v>
+        <v>103078</v>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 19*19*19cm</t>
+          <t>Bag chocolala 90*45*35cm</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -16109,17 +16109,17 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>103072.jpg</t>
+          <t>103078.jpg</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
-        <v>103073</v>
+        <v>103060</v>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 29*12*15cm (1kg) (1007-3)</t>
+          <t>Bag 19cm x 10cm x 15cm</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
@@ -16144,17 +16144,17 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>103073.jpg</t>
+          <t>103060.jpg</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
-        <v>103074</v>
+        <v>103061</v>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 29*29*29cm</t>
+          <t>Bag 24cm x 13cm x 23cm</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -16179,17 +16179,17 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>103074.jpg</t>
+          <t>103061.jpg</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
-        <v>103075</v>
+        <v>103079</v>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 34*34*34cm</t>
+          <t>Bag chocolala green 35*24.5*12.8cm (s) (1007-1)</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
@@ -16214,17 +16214,17 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>103075.jpg</t>
+          <t>103079.jpg</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
-        <v>103076</v>
+        <v>103080</v>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 50*40*40cm</t>
+          <t>Bag chocolala green 40*27*14cm (b) (1007-2)</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -16249,104 +16249,106 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>103076.jpg</t>
+          <t>103080.jpg</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
-        <v>103077</v>
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>115404</t>
+        </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 57*36*40cm</t>
+          <t>Custmoized Egg</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Customized</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Special collection</t>
         </is>
       </c>
       <c r="E437" s="2" t="n"/>
       <c r="F437" s="2" t="n"/>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>CARTON</t>
+      <c r="G437" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H437" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I437" s="2" t="inlineStr">
-        <is>
-          <t>103077.jpg</t>
-        </is>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="I437" s="2" t="n"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
-        <v>103078</v>
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>106190</t>
+        </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala 90*45*35cm</t>
+          <t>Majdool Dates with nuts</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E438" s="2" t="n"/>
       <c r="F438" s="2" t="n"/>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>CARTON</t>
+      <c r="G438" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H438" s="3" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>103078.jpg</t>
+          <t>custom-majdool-dates-with-nuts.jpg</t>
         </is>
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
-        <v>103060</v>
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>102164</t>
+        </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>Bag 19cm x 10cm x 15cm</t>
+          <t>Sticky Notes 75*75</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="E439" s="2" t="n"/>
       <c r="F439" s="2" t="n"/>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>CARTON</t>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H439" s="3" t="n">
@@ -16354,34 +16356,36 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>103060.jpg</t>
+          <t>102164.jpg</t>
         </is>
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
-        <v>103061</v>
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>107959</t>
+        </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>Bag 24cm x 13cm x 23cm</t>
+          <t>Sticky Notes Small</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="E440" s="2" t="n"/>
       <c r="F440" s="2" t="n"/>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>CARTON</t>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H440" s="3" t="n">
@@ -16389,34 +16393,36 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>103061.jpg</t>
+          <t>107959.jpg</t>
         </is>
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
-        <v>103079</v>
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>102073</t>
+        </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala green 35*24.5*12.8cm (s) (1007-1)</t>
+          <t>Binder Clip Small 19mm</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="E441" s="2" t="n"/>
       <c r="F441" s="2" t="n"/>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>CARTON</t>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H441" s="3" t="n">
@@ -16424,34 +16430,36 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>103079.jpg</t>
+          <t>102073.jpg</t>
         </is>
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
-        <v>103080</v>
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>102074</t>
+        </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Bag chocolala green 40*27*14cm (b) (1007-2)</t>
+          <t>Box File Big</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="E442" s="2" t="n"/>
       <c r="F442" s="2" t="n"/>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>CARTON</t>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H442" s="3" t="n">
@@ -16459,89 +16467,93 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>103080.jpg</t>
+          <t>102074.jpg</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>115404</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>Custmoized Egg</t>
+          <t>Double Sided Tape 4cm</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>Customized</t>
+          <t>Tapes</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Special collection</t>
+          <t>Decoration</t>
         </is>
       </c>
       <c r="E443" s="2" t="n"/>
       <c r="F443" s="2" t="n"/>
-      <c r="G443" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H443" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="I443" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>102116.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>106190</t>
+          <t>102144</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>Majdool Dates with nuts</t>
+          <t>Polyfix Instant Glue 20ml</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Stationery</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Dry fruit</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="E444" s="2" t="n"/>
       <c r="F444" s="2" t="n"/>
-      <c r="G444" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>PCS</t>
         </is>
       </c>
       <c r="H444" s="3" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>custom-majdool-dates-with-nuts.jpg</t>
+          <t>102144.PNG</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>102164</t>
+          <t>105735</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>Sticky Notes 75*75</t>
+          <t>Sharpener</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
@@ -16566,246 +16578,246 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>102164.jpg</t>
+          <t>105735.jpg</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>107959</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>Sticky Notes Small</t>
-        </is>
-      </c>
-      <c r="C446" s="2" t="inlineStr">
-        <is>
-          <t>Stationery</t>
+          <t>Premium Belgium Wrapped Brown Kitkat Kg</t>
+        </is>
+      </c>
+      <c r="C446" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E446" s="2" t="n"/>
       <c r="F446" s="2" t="n"/>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
+      <c r="G446" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H446" s="3" t="n">
-        <v>0</v>
+        <v>178.5</v>
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>107959.jpg</t>
+          <t>112613.jpg</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>102073</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>Binder Clip Small 19mm</t>
+          <t>Premium Belgium Open Brown Royal Caramel Bar Caramel &amp; Chocolate Kg</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E447" s="2" t="n"/>
       <c r="F447" s="2" t="n"/>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
+      <c r="G447" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H447" s="3" t="n">
-        <v>0</v>
+        <v>136.75</v>
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>102073.jpg</t>
+          <t>111393.jpg</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>Box File Big</t>
-        </is>
-      </c>
-      <c r="C448" s="2" t="inlineStr">
-        <is>
-          <t>Stationery</t>
+          <t>Premium Belgium Open Gold Choco Squirrel Plain &amp; Belgian Kg</t>
+        </is>
+      </c>
+      <c r="C448" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E448" s="2" t="n"/>
       <c r="F448" s="2" t="n"/>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
+      <c r="G448" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H448" s="3" t="n">
-        <v>0</v>
+        <v>141.75</v>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>102074.jpg</t>
+          <t>111130.jpg</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>102116</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>Double Sided Tape 4cm</t>
+          <t>Premium Belgium Open Brown Cup Almond Nutella Kg</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>Tapes</t>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>Decoration</t>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E449" s="2" t="n"/>
       <c r="F449" s="2" t="n"/>
-      <c r="G449" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
+      <c r="G449" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H449" s="3" t="n">
-        <v>0</v>
+        <v>136.75</v>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>102116.jpg</t>
+          <t>113454.jpg</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>102144</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>Polyfix Instant Glue 20ml</t>
+          <t>Premium Belgium Open Brown Cup Nutella Hazelnut Kg</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E450" s="2" t="n"/>
       <c r="F450" s="2" t="n"/>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
+      <c r="G450" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H450" s="3" t="n">
-        <v>0</v>
+        <v>136.75</v>
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>102144.PNG</t>
+          <t>114199.jpg</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>105735</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>Sharpener</t>
+          <t>Premium Belgium Open Brown Mushroom Jandoya Almond Kg</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>Stationery</t>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E451" s="2" t="n"/>
       <c r="F451" s="2" t="n"/>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>PCS</t>
+      <c r="G451" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
         </is>
       </c>
       <c r="H451" s="3" t="n">
-        <v>0</v>
+        <v>136.75</v>
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>105735.jpg</t>
+          <t>111975.jpg</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>100382</t>
+          <t>100414</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Wrapped Brown Kitkat Kg</t>
-        </is>
-      </c>
-      <c r="C452" s="15" t="inlineStr">
-        <is>
-          <t>Belgium wrapped</t>
+          <t>Premium Belgium Open Brown Nutella Caramel Kg</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -16821,11 +16833,11 @@
         </is>
       </c>
       <c r="H452" s="3" t="n">
-        <v>178.5</v>
+        <v>136.75</v>
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>112613.jpg</t>
+          <t>111976.jpg</t>
         </is>
       </c>
     </row>
@@ -16837,7 +16849,7 @@
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Royal Caramel Bar Caramel &amp; Chocolate Kg</t>
+          <t>Premium Belgium Open Brown Oman Chips Kg</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
@@ -16862,24 +16874,24 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>111393.jpg</t>
+          <t>112497.jpg</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100415</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Gold Choco Squirrel Plain &amp; Belgian Kg</t>
-        </is>
-      </c>
-      <c r="C454" s="15" t="inlineStr">
-        <is>
-          <t>Belgium wrapped</t>
+          <t>Premium Belgium Open Brown Royal Bar Feuilletine Biscuit &amp; Chocolate Kg</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -16895,28 +16907,28 @@
         </is>
       </c>
       <c r="H454" s="3" t="n">
-        <v>141.75</v>
+        <v>136.75</v>
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>111130.jpg</t>
+          <t>111392.jpg</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>108656</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Cup Almond Nutella Kg</t>
-        </is>
-      </c>
-      <c r="C455" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>Belgium Square Wafer With Chocolate Print Kg</t>
+        </is>
+      </c>
+      <c r="C455" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -16932,28 +16944,28 @@
         </is>
       </c>
       <c r="H455" s="3" t="n">
-        <v>136.75</v>
+        <v>178.5</v>
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>113454.jpg</t>
+          <t>108656.jpg</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Cup Nutella Hazelnut Kg</t>
-        </is>
-      </c>
-      <c r="C456" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>Wrapped Belgium Baby Boy mix</t>
+        </is>
+      </c>
+      <c r="C456" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -16969,28 +16981,24 @@
         </is>
       </c>
       <c r="H456" s="3" t="n">
-        <v>136.75</v>
-      </c>
-      <c r="I456" s="2" t="inlineStr">
-        <is>
-          <t>114199.jpg</t>
-        </is>
-      </c>
+        <v>141.75</v>
+      </c>
+      <c r="I456" s="2" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Mushroom Jandoya Almond Kg</t>
-        </is>
-      </c>
-      <c r="C457" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>Wrapped Belgium Baby Boy Slice Dirham</t>
+        </is>
+      </c>
+      <c r="C457" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -17006,28 +17014,24 @@
         </is>
       </c>
       <c r="H457" s="3" t="n">
-        <v>136.75</v>
-      </c>
-      <c r="I457" s="2" t="inlineStr">
-        <is>
-          <t>111975.jpg</t>
-        </is>
-      </c>
+        <v>141.75</v>
+      </c>
+      <c r="I457" s="2" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Nutella Caramel Kg</t>
-        </is>
-      </c>
-      <c r="C458" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>Wrapped Belgium Baby Girl mix</t>
+        </is>
+      </c>
+      <c r="C458" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -17043,28 +17047,24 @@
         </is>
       </c>
       <c r="H458" s="3" t="n">
-        <v>136.75</v>
-      </c>
-      <c r="I458" s="2" t="inlineStr">
-        <is>
-          <t>111976.jpg</t>
-        </is>
-      </c>
+        <v>141.75</v>
+      </c>
+      <c r="I458" s="2" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>100414</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Oman Chips Kg</t>
-        </is>
-      </c>
-      <c r="C459" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>Wrapped Belgium Baby Girl Slice Dirham</t>
+        </is>
+      </c>
+      <c r="C459" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -17080,28 +17080,24 @@
         </is>
       </c>
       <c r="H459" s="3" t="n">
-        <v>136.75</v>
-      </c>
-      <c r="I459" s="2" t="inlineStr">
-        <is>
-          <t>112497.jpg</t>
-        </is>
-      </c>
+        <v>141.75</v>
+      </c>
+      <c r="I459" s="2" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>100415</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Premium Belgium Open Brown Royal Bar Feuilletine Biscuit &amp; Chocolate Kg</t>
-        </is>
-      </c>
-      <c r="C460" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>Big Sequare Belgium wrapped</t>
+        </is>
+      </c>
+      <c r="C460" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -17117,33 +17113,29 @@
         </is>
       </c>
       <c r="H460" s="3" t="n">
-        <v>136.75</v>
-      </c>
-      <c r="I460" s="2" t="inlineStr">
-        <is>
-          <t>111392.jpg</t>
-        </is>
-      </c>
+        <v>141.75</v>
+      </c>
+      <c r="I460" s="2" t="n"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="inlineStr">
-        <is>
-          <t>108656</t>
+      <c r="A461" s="15" t="inlineStr">
+        <is>
+          <t>106191</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>Belgium Square Wafer With Chocolate Print Kg</t>
+          <t>Premium apricoat with almond kg</t>
         </is>
       </c>
       <c r="C461" s="15" t="inlineStr">
         <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D461" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
+          <t>Apricoat</t>
+        </is>
+      </c>
+      <c r="D461" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E461" s="2" t="n"/>
@@ -17154,33 +17146,33 @@
         </is>
       </c>
       <c r="H461" s="3" t="n">
-        <v>178.5</v>
+        <v>147</v>
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>108656.jpg</t>
+          <t>111221.jpg</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="inlineStr">
-        <is>
-          <t>100382</t>
+      <c r="A462" s="15" t="inlineStr">
+        <is>
+          <t>106191</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>Wrapped Belgium Baby Boy mix</t>
+          <t>Premium apricoat with cashew kg</t>
         </is>
       </c>
       <c r="C462" s="15" t="inlineStr">
         <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D462" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
+          <t>Apricoat</t>
+        </is>
+      </c>
+      <c r="D462" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E462" s="2" t="n"/>
@@ -17191,29 +17183,33 @@
         </is>
       </c>
       <c r="H462" s="3" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="I462" s="2" t="n"/>
+        <v>147</v>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>111252.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="inlineStr">
-        <is>
-          <t>100382</t>
-        </is>
-      </c>
-      <c r="B463" s="2" t="inlineStr">
-        <is>
-          <t>Wrapped Belgium Baby Boy Slice Dirham</t>
+      <c r="A463" s="15" t="inlineStr">
+        <is>
+          <t>106191</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Premium apricoat with hazelnut kg</t>
         </is>
       </c>
       <c r="C463" s="15" t="inlineStr">
         <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D463" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
+          <t>Apricoat</t>
+        </is>
+      </c>
+      <c r="D463" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E463" s="2" t="n"/>
@@ -17224,29 +17220,33 @@
         </is>
       </c>
       <c r="H463" s="3" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="I463" s="2" t="n"/>
+        <v>147</v>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>111253.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="inlineStr">
-        <is>
-          <t>100382</t>
-        </is>
-      </c>
-      <c r="B464" s="2" t="inlineStr">
-        <is>
-          <t>Wrapped Belgium Baby Girl mix</t>
+      <c r="A464" s="15" t="inlineStr">
+        <is>
+          <t>106191</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Premium apricoat with walnut kg</t>
         </is>
       </c>
       <c r="C464" s="15" t="inlineStr">
         <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D464" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
+          <t>Apricoat</t>
+        </is>
+      </c>
+      <c r="D464" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E464" s="2" t="n"/>
@@ -17257,29 +17257,33 @@
         </is>
       </c>
       <c r="H464" s="3" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="I464" s="2" t="n"/>
+        <v>147</v>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>111255.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="inlineStr">
-        <is>
-          <t>100382</t>
-        </is>
-      </c>
-      <c r="B465" s="2" t="inlineStr">
-        <is>
-          <t>Wrapped Belgium Baby Girl Slice Dirham</t>
+      <c r="A465" s="15" t="inlineStr">
+        <is>
+          <t>106191</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Premium apricoat with white walnut kg</t>
         </is>
       </c>
       <c r="C465" s="15" t="inlineStr">
         <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D465" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
+          <t>Apricoat</t>
+        </is>
+      </c>
+      <c r="D465" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
         </is>
       </c>
       <c r="E465" s="2" t="n"/>
@@ -17290,235 +17294,201 @@
         </is>
       </c>
       <c r="H465" s="3" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="I465" s="2" t="n"/>
-    </row>
-    <row r="466">
-      <c r="A466" s="2" t="inlineStr">
-        <is>
-          <t>100382</t>
-        </is>
-      </c>
-      <c r="B466" s="2" t="inlineStr">
-        <is>
-          <t>Big Sequare Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="C466" s="15" t="inlineStr">
-        <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D466" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
-        </is>
-      </c>
-      <c r="E466" s="2" t="n"/>
-      <c r="F466" s="2" t="n"/>
-      <c r="G466" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H466" s="3" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="I466" s="2" t="n"/>
-    </row>
-    <row r="467">
-      <c r="A467" s="15" t="inlineStr">
-        <is>
-          <t>106191</t>
-        </is>
-      </c>
-      <c r="B467" s="2" t="inlineStr">
-        <is>
-          <t>Premium apricoat with almond kg</t>
-        </is>
-      </c>
-      <c r="C467" s="15" t="inlineStr">
-        <is>
-          <t>Apricoat</t>
-        </is>
-      </c>
-      <c r="D467" s="15" t="inlineStr">
-        <is>
-          <t>Dry fruit</t>
-        </is>
-      </c>
-      <c r="E467" s="2" t="n"/>
-      <c r="F467" s="2" t="n"/>
-      <c r="G467" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H467" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="I467" s="2" t="inlineStr">
-        <is>
-          <t>111221.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" s="15" t="inlineStr">
-        <is>
-          <t>106191</t>
-        </is>
-      </c>
-      <c r="B468" s="2" t="inlineStr">
-        <is>
-          <t>Premium apricoat with cashew kg</t>
-        </is>
-      </c>
-      <c r="C468" s="15" t="inlineStr">
-        <is>
-          <t>Apricoat</t>
-        </is>
-      </c>
-      <c r="D468" s="15" t="inlineStr">
-        <is>
-          <t>Dry fruit</t>
-        </is>
-      </c>
-      <c r="E468" s="2" t="n"/>
-      <c r="F468" s="2" t="n"/>
-      <c r="G468" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H468" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="I468" s="2" t="inlineStr">
-        <is>
-          <t>111252.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" s="15" t="inlineStr">
-        <is>
-          <t>106191</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>Premium apricoat with hazelnut kg</t>
-        </is>
-      </c>
-      <c r="C469" s="15" t="inlineStr">
-        <is>
-          <t>Apricoat</t>
-        </is>
-      </c>
-      <c r="D469" s="15" t="inlineStr">
-        <is>
-          <t>Dry fruit</t>
-        </is>
-      </c>
-      <c r="E469" s="2" t="n"/>
-      <c r="F469" s="2" t="n"/>
-      <c r="G469" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H469" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="I469" s="2" t="inlineStr">
-        <is>
-          <t>111253.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" s="15" t="inlineStr">
-        <is>
-          <t>106191</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>Premium apricoat with walnut kg</t>
-        </is>
-      </c>
-      <c r="C470" s="15" t="inlineStr">
-        <is>
-          <t>Apricoat</t>
-        </is>
-      </c>
-      <c r="D470" s="15" t="inlineStr">
-        <is>
-          <t>Dry fruit</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="n"/>
-      <c r="F470" s="2" t="n"/>
-      <c r="G470" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H470" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="I470" s="2" t="inlineStr">
-        <is>
-          <t>111255.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" s="15" t="inlineStr">
-        <is>
-          <t>106191</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>Premium apricoat with white walnut kg</t>
-        </is>
-      </c>
-      <c r="C471" s="15" t="inlineStr">
-        <is>
-          <t>Apricoat</t>
-        </is>
-      </c>
-      <c r="D471" s="15" t="inlineStr">
-        <is>
-          <t>Dry fruit</t>
-        </is>
-      </c>
-      <c r="E471" s="2" t="n"/>
-      <c r="F471" s="2" t="n"/>
-      <c r="G471" s="8" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H471" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="I471" s="2" t="inlineStr">
+      <c r="I465" s="2" t="inlineStr">
         <is>
           <t>115250.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" customFormat="1" s="18">
+      <c r="A466" s="18" t="n">
+        <v>110486</v>
+      </c>
+      <c r="B466" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLC BOX 30X25X12 CM WITH PAPER HOLDER</t>
+        </is>
+      </c>
+      <c r="C466" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D466" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G466" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>110486.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" customFormat="1" s="18">
+      <c r="A467" s="18" t="n">
+        <v>110487</v>
+      </c>
+      <c r="B467" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLC BOX 30X25X7 CM WITH PAPER HOLDER</t>
+        </is>
+      </c>
+      <c r="C467" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D467" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G467" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>110487.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" customFormat="1" s="18">
+      <c r="A468" s="18" t="n">
+        <v>109806</v>
+      </c>
+      <c r="B468" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLIC TRAY SMALL 32.5X20X4CM</t>
+        </is>
+      </c>
+      <c r="C468" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D468" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G468" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>109806.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" customFormat="1" s="18">
+      <c r="A469" s="18" t="n">
+        <v>109807</v>
+      </c>
+      <c r="B469" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLIC TRAY MEDIUM 36.3X22.7X4.5CM</t>
+        </is>
+      </c>
+      <c r="C469" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D469" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G469" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>109807.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" customFormat="1" s="18">
+      <c r="A470" s="18" t="n">
+        <v>107808</v>
+      </c>
+      <c r="B470" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLIC TRAY LARGE 40X25X5CM</t>
+        </is>
+      </c>
+      <c r="C470" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D470" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G470" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>109808.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" customFormat="1" s="18">
+      <c r="A471" s="18" t="n">
+        <v>110483</v>
+      </c>
+      <c r="B471" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX 18X15X4.5CM</t>
+        </is>
+      </c>
+      <c r="C471" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D471" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G471" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>110483.jpg</t>
         </is>
       </c>
     </row>
     <row r="472" customFormat="1" s="18">
       <c r="A472" s="18" t="n">
-        <v>110486</v>
+        <v>108081</v>
       </c>
       <c r="B472" s="18" t="inlineStr">
         <is>
-          <t>ACRYLC BOX 30X25X12 CM WITH PAPER HOLDER</t>
+          <t>ACRYLIC BOX 23X50X11 WITH PARTITION EMPTY</t>
         </is>
       </c>
       <c r="C472" s="18" t="inlineStr">
@@ -17538,17 +17508,17 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>110486.jpg</t>
+          <t>108081.jpg</t>
         </is>
       </c>
     </row>
     <row r="473" customFormat="1" s="18">
       <c r="A473" s="18" t="n">
-        <v>110487</v>
+        <v>110608</v>
       </c>
       <c r="B473" s="18" t="inlineStr">
         <is>
-          <t>ACRYLC BOX 30X25X7 CM WITH PAPER HOLDER</t>
+          <t>ACRYLIC BOX 30X8X6CM</t>
         </is>
       </c>
       <c r="C473" s="18" t="inlineStr">
@@ -17568,17 +17538,17 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>110487.jpg</t>
+          <t>110608.jpg</t>
         </is>
       </c>
     </row>
     <row r="474" customFormat="1" s="18">
       <c r="A474" s="18" t="n">
-        <v>109806</v>
+        <v>109042</v>
       </c>
       <c r="B474" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY SMALL 32.5X20X4CM</t>
+          <t>ACRYLIC BOX WITH ACRYLIC GOLD DESIGN IN COVER 21X14X4CM</t>
         </is>
       </c>
       <c r="C474" s="18" t="inlineStr">
@@ -17598,17 +17568,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>109806.jpg</t>
+          <t>109042.jpg</t>
         </is>
       </c>
     </row>
     <row r="475" customFormat="1" s="18">
       <c r="A475" s="18" t="n">
-        <v>109807</v>
+        <v>110509</v>
       </c>
       <c r="B475" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY MEDIUM 36.3X22.7X4.5CM</t>
+          <t>FOREX AND ACRYLIC BOX 57X27X3CM</t>
         </is>
       </c>
       <c r="C475" s="18" t="inlineStr">
@@ -17628,17 +17598,17 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>109807.jpg</t>
+          <t>110509.jpg</t>
         </is>
       </c>
     </row>
     <row r="476" customFormat="1" s="18">
       <c r="A476" s="18" t="n">
-        <v>107808</v>
+        <v>109044</v>
       </c>
       <c r="B476" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY LARGE 40X25X5CM</t>
+          <t>ACRYLIC BOX WITH CHAIN HANDLE 21X10X16 CM EMPTY</t>
         </is>
       </c>
       <c r="C476" s="18" t="inlineStr">
@@ -17658,17 +17628,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>109808.jpg</t>
+          <t>109044.jpg</t>
         </is>
       </c>
     </row>
     <row r="477" customFormat="1" s="18">
       <c r="A477" s="18" t="n">
-        <v>110483</v>
+        <v>108972</v>
       </c>
       <c r="B477" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 18X15X4.5CM</t>
+          <t>ACRYLIC BOX WITH CHAIN HANDLE</t>
         </is>
       </c>
       <c r="C477" s="18" t="inlineStr">
@@ -17688,17 +17658,17 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>110483.jpg</t>
+          <t>108972.jpg</t>
         </is>
       </c>
     </row>
     <row r="478" customFormat="1" s="18">
       <c r="A478" s="18" t="n">
-        <v>108081</v>
+        <v>110045</v>
       </c>
       <c r="B478" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 23X50X11 WITH PARTITION EMPTY</t>
+          <t>ACRYLIC TRAY CHOCOLALA 40X20X34CM</t>
         </is>
       </c>
       <c r="C478" s="18" t="inlineStr">
@@ -17718,17 +17688,17 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>108081.jpg</t>
+          <t>110045.jpg</t>
         </is>
       </c>
     </row>
     <row r="479" customFormat="1" s="18">
       <c r="A479" s="18" t="n">
-        <v>110608</v>
+        <v>110047</v>
       </c>
       <c r="B479" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 30X8X6CM</t>
+          <t>GOLD RECTANGLE HANDLE ACRYLIC BOX (30X20X30CM)</t>
         </is>
       </c>
       <c r="C479" s="18" t="inlineStr">
@@ -17748,17 +17718,17 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>110608.jpg</t>
+          <t>110047.jpg</t>
         </is>
       </c>
     </row>
     <row r="480" customFormat="1" s="18">
       <c r="A480" s="18" t="n">
-        <v>109042</v>
+        <v>110046</v>
       </c>
       <c r="B480" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH ACRYLIC GOLD DESIGN IN COVER 21X14X4CM</t>
+          <t>GOLD HEART HANDLE ACRYLIC BAG-BOX (30X20X39.5)</t>
         </is>
       </c>
       <c r="C480" s="18" t="inlineStr">
@@ -17778,17 +17748,17 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>109042.jpg</t>
+          <t>110046.jpg</t>
         </is>
       </c>
     </row>
     <row r="481" customFormat="1" s="18">
       <c r="A481" s="18" t="n">
-        <v>110509</v>
+        <v>110723</v>
       </c>
       <c r="B481" s="18" t="inlineStr">
         <is>
-          <t>FOREX AND ACRYLIC BOX 57X27X3CM</t>
+          <t>ACRYLIC BOX 25X23X11CM</t>
         </is>
       </c>
       <c r="C481" s="18" t="inlineStr">
@@ -17808,17 +17778,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>110509.jpg</t>
+          <t>110723.jpg</t>
         </is>
       </c>
     </row>
     <row r="482" customFormat="1" s="18">
       <c r="A482" s="18" t="n">
-        <v>109044</v>
+        <v>109862</v>
       </c>
       <c r="B482" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH CHAIN HANDLE 21X10X16 CM EMPTY</t>
+          <t>ACRYLIC BOX WITH PARTITION 42.5X16X3.5CM</t>
         </is>
       </c>
       <c r="C482" s="18" t="inlineStr">
@@ -17838,17 +17808,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>109044.jpg</t>
+          <t>109862.jpg</t>
         </is>
       </c>
     </row>
     <row r="483" customFormat="1" s="18">
       <c r="A483" s="18" t="n">
-        <v>108972</v>
+        <v>110321</v>
       </c>
       <c r="B483" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH CHAIN HANDLE</t>
+          <t>CHOCOLA PURE ACRYLIC BOX W 9 PARTITION 90X39X5CM</t>
         </is>
       </c>
       <c r="C483" s="18" t="inlineStr">
@@ -17868,17 +17838,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>108972.jpg</t>
+          <t>110321.jpg</t>
         </is>
       </c>
     </row>
     <row r="484" customFormat="1" s="18">
       <c r="A484" s="18" t="n">
-        <v>110045</v>
+        <v>110435</v>
       </c>
       <c r="B484" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY CHOCOLALA 40X20X34CM</t>
+          <t>ACRYLIC BOX 16X16X4CM</t>
         </is>
       </c>
       <c r="C484" s="18" t="inlineStr">
@@ -17898,17 +17868,17 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>110045.jpg</t>
+          <t>110435.jpg</t>
         </is>
       </c>
     </row>
     <row r="485" customFormat="1" s="18">
       <c r="A485" s="18" t="n">
-        <v>110047</v>
+        <v>110660</v>
       </c>
       <c r="B485" s="18" t="inlineStr">
         <is>
-          <t>GOLD RECTANGLE HANDLE ACRYLIC BOX (30X20X30CM)</t>
+          <t>ACRYLIC BOX 30X16.5X9CM 20 PART. W/ CHOCO BOARD</t>
         </is>
       </c>
       <c r="C485" s="18" t="inlineStr">
@@ -17928,17 +17898,17 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>110047.jpg</t>
+          <t>110660.jpg</t>
         </is>
       </c>
     </row>
     <row r="486" customFormat="1" s="18">
       <c r="A486" s="18" t="n">
-        <v>110046</v>
+        <v>110436</v>
       </c>
       <c r="B486" s="18" t="inlineStr">
         <is>
-          <t>GOLD HEART HANDLE ACRYLIC BAG-BOX (30X20X39.5)</t>
+          <t>ACRYLIC BOX 26X18X6CM</t>
         </is>
       </c>
       <c r="C486" s="18" t="inlineStr">
@@ -17958,17 +17928,17 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>110046.jpg</t>
+          <t>110436.jpg</t>
         </is>
       </c>
     </row>
     <row r="487" customFormat="1" s="18">
       <c r="A487" s="18" t="n">
-        <v>110723</v>
+        <v>108954</v>
       </c>
       <c r="B487" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 25X23X11CM</t>
+          <t>ACRYLIC BOX 35X28X5CM</t>
         </is>
       </c>
       <c r="C487" s="18" t="inlineStr">
@@ -17988,17 +17958,17 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>110723.jpg</t>
+          <t>108954.jpg</t>
         </is>
       </c>
     </row>
     <row r="488" customFormat="1" s="18">
       <c r="A488" s="18" t="n">
-        <v>109862</v>
+        <v>110434</v>
       </c>
       <c r="B488" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH PARTITION 42.5X16X3.5CM</t>
+          <t>ACRYLIC BOX CLEAR 28X25X5CM EMPTY</t>
         </is>
       </c>
       <c r="C488" s="18" t="inlineStr">
@@ -18018,17 +17988,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>109862.jpg</t>
+          <t>110434.jpg</t>
         </is>
       </c>
     </row>
     <row r="489" customFormat="1" s="18">
       <c r="A489" s="18" t="n">
-        <v>110321</v>
+        <v>100674</v>
       </c>
       <c r="B489" s="18" t="inlineStr">
         <is>
-          <t>CHOCOLA PURE ACRYLIC BOX W 9 PARTITION 90X39X5CM</t>
+          <t>ACRYLIC BOXES CLEAR W/ COLORED BASE EMPTY</t>
         </is>
       </c>
       <c r="C489" s="18" t="inlineStr">
@@ -18048,17 +18018,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>110321.jpg</t>
+          <t>100674.PNG</t>
         </is>
       </c>
     </row>
     <row r="490" customFormat="1" s="18">
       <c r="A490" s="18" t="n">
-        <v>110435</v>
+        <v>110301</v>
       </c>
       <c r="B490" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 16X16X4CM</t>
+          <t>ACRYLIC BOX 21X21X5CM</t>
         </is>
       </c>
       <c r="C490" s="18" t="inlineStr">
@@ -18078,17 +18048,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>110435.jpg</t>
+          <t>110301.jpg</t>
         </is>
       </c>
     </row>
     <row r="491" customFormat="1" s="18">
       <c r="A491" s="18" t="n">
-        <v>110660</v>
+        <v>110007</v>
       </c>
       <c r="B491" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 30X16.5X9CM 20 PART. W/ CHOCO BOARD</t>
+          <t>ACRYLIC BOX 50x20x5CM WHITE EMPTY</t>
         </is>
       </c>
       <c r="C491" s="18" t="inlineStr">
@@ -18108,17 +18078,17 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>110660.jpg</t>
+          <t>110007.jpg</t>
         </is>
       </c>
     </row>
     <row r="492" customFormat="1" s="18">
       <c r="A492" s="18" t="n">
-        <v>110436</v>
+        <v>108658</v>
       </c>
       <c r="B492" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 26X18X6CM</t>
+          <t>ACRYLIC BOX 60x21x4cm</t>
         </is>
       </c>
       <c r="C492" s="18" t="inlineStr">
@@ -18138,17 +18108,17 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>110436.jpg</t>
+          <t>112420.jpg</t>
         </is>
       </c>
     </row>
     <row r="493" customFormat="1" s="18">
       <c r="A493" s="18" t="n">
-        <v>108954</v>
+        <v>108383</v>
       </c>
       <c r="B493" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 35X28X5CM</t>
+          <t>HEXAGON DESIGN ACRYLIC BOX SMALL 30*26*5CM EMPTY</t>
         </is>
       </c>
       <c r="C493" s="18" t="inlineStr">
@@ -18168,17 +18138,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>108954.jpg</t>
+          <t>108383.jpg</t>
         </is>
       </c>
     </row>
     <row r="494" customFormat="1" s="18">
       <c r="A494" s="18" t="n">
-        <v>110434</v>
+        <v>108385</v>
       </c>
       <c r="B494" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX CLEAR 28X25X5CM EMPTY</t>
+          <t>ACRYLIC BOX WITH STAND MEDIUM 40.5*35*5 CM EMPTY</t>
         </is>
       </c>
       <c r="C494" s="18" t="inlineStr">
@@ -18198,17 +18168,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>110434.jpg</t>
+          <t>108385.jpg</t>
         </is>
       </c>
     </row>
     <row r="495" customFormat="1" s="18">
       <c r="A495" s="18" t="n">
-        <v>100674</v>
+        <v>108386</v>
       </c>
       <c r="B495" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOXES CLEAR W/ COLORED BASE EMPTY</t>
+          <t>ACRYLIC BOX WITH STAND LARGE 51.5*44.5*5CM</t>
         </is>
       </c>
       <c r="C495" s="18" t="inlineStr">
@@ -18228,17 +18198,17 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>100674.PNG</t>
+          <t>108386.jpg</t>
         </is>
       </c>
     </row>
     <row r="496" customFormat="1" s="18">
       <c r="A496" s="18" t="n">
-        <v>110301</v>
+        <v>105755</v>
       </c>
       <c r="B496" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 21X21X5CM</t>
+          <t>ACRYLIC DRAGEEE BOX EMPTY</t>
         </is>
       </c>
       <c r="C496" s="18" t="inlineStr">
@@ -18258,17 +18228,17 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>110301.jpg</t>
+          <t>105755.jpg</t>
         </is>
       </c>
     </row>
     <row r="497" customFormat="1" s="18">
       <c r="A497" s="18" t="n">
-        <v>110007</v>
+        <v>100678</v>
       </c>
       <c r="B497" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 50x20x5CM WHITE EMPTY</t>
+          <t>CHOCOLALA RECT. ACRYLIC BOX 23X78X6 EMPTY</t>
         </is>
       </c>
       <c r="C497" s="18" t="inlineStr">
@@ -18288,17 +18258,17 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>110007.jpg</t>
+          <t>100678.png</t>
         </is>
       </c>
     </row>
     <row r="498" customFormat="1" s="18">
       <c r="A498" s="18" t="n">
-        <v>108658</v>
+        <v>107554</v>
       </c>
       <c r="B498" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 60x21x4cm</t>
+          <t>ACRYLIC BOX 50*23*11CM (EMPTY)</t>
         </is>
       </c>
       <c r="C498" s="18" t="inlineStr">
@@ -18318,17 +18288,17 @@
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>112420.jpg</t>
+          <t>107554.jpg</t>
         </is>
       </c>
     </row>
     <row r="499" customFormat="1" s="18">
       <c r="A499" s="18" t="n">
-        <v>108383</v>
+        <v>110610</v>
       </c>
       <c r="B499" s="18" t="inlineStr">
         <is>
-          <t>HEXAGON DESIGN ACRYLIC BOX SMALL 30*26*5CM EMPTY</t>
+          <t>ACRYLIC BOX BUTTERFLY STAND 40X16X16CM</t>
         </is>
       </c>
       <c r="C499" s="18" t="inlineStr">
@@ -18348,25 +18318,25 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>108383.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="500" customFormat="1" s="18">
-      <c r="A500" s="18" t="n">
-        <v>108385</v>
-      </c>
-      <c r="B500" s="18" t="inlineStr">
-        <is>
-          <t>ACRYLIC BOX WITH STAND MEDIUM 40.5*35*5 CM EMPTY</t>
-        </is>
-      </c>
-      <c r="C500" s="18" t="inlineStr">
+          <t>110610.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>110936</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX WITH BLACK SURFACE DESIGN 35X28X5CM</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D500" s="18" t="inlineStr">
+      <c r="D500" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
@@ -18378,25 +18348,25 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>108385.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="501" customFormat="1" s="18">
-      <c r="A501" s="18" t="n">
-        <v>108386</v>
-      </c>
-      <c r="B501" s="18" t="inlineStr">
-        <is>
-          <t>ACRYLIC BOX WITH STAND LARGE 51.5*44.5*5CM</t>
-        </is>
-      </c>
-      <c r="C501" s="18" t="inlineStr">
+          <t>110936.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>110933</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX 27X20X5CM WHITE AND CLEAR</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D501" s="18" t="inlineStr">
+      <c r="D501" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
@@ -18408,25 +18378,25 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>108386.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="502" customFormat="1" s="18">
-      <c r="A502" s="18" t="n">
-        <v>105755</v>
-      </c>
-      <c r="B502" s="18" t="inlineStr">
-        <is>
-          <t>ACRYLIC DRAGEEE BOX EMPTY</t>
-        </is>
-      </c>
-      <c r="C502" s="18" t="inlineStr">
+          <t>110933.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>110894</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX 27X24X5CM</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D502" s="18" t="inlineStr">
+      <c r="D502" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
@@ -18438,25 +18408,25 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>105755.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="503" customFormat="1" s="18">
-      <c r="A503" s="18" t="n">
-        <v>100678</v>
-      </c>
-      <c r="B503" s="18" t="inlineStr">
-        <is>
-          <t>CHOCOLALA RECT. ACRYLIC BOX 23X78X6 EMPTY</t>
-        </is>
-      </c>
-      <c r="C503" s="18" t="inlineStr">
+          <t>110894.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>110723</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX 25X23X11CM</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D503" s="18" t="inlineStr">
+      <c r="D503" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
@@ -18468,25 +18438,25 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>100678.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="504" customFormat="1" s="18">
-      <c r="A504" s="18" t="n">
-        <v>107554</v>
-      </c>
-      <c r="B504" s="18" t="inlineStr">
-        <is>
-          <t>ACRYLIC BOX 50*23*11CM (EMPTY)</t>
-        </is>
-      </c>
-      <c r="C504" s="18" t="inlineStr">
+          <t>110723.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>110782</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>ACRYLIC NUTS BOX WITH 8 PART 37X19X8CM EMPTY VERSION 2</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D504" s="18" t="inlineStr">
+      <c r="D504" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
@@ -18498,25 +18468,25 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>107554.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="505" customFormat="1" s="18">
-      <c r="A505" s="18" t="n">
-        <v>110610</v>
-      </c>
-      <c r="B505" s="18" t="inlineStr">
-        <is>
-          <t>ACRYLIC BOX BUTTERFLY STAND 40X16X16CM</t>
-        </is>
-      </c>
-      <c r="C505" s="18" t="inlineStr">
+          <t>110782.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>110834</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX W/6 PART 35X25X3.5CM</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D505" s="18" t="inlineStr">
+      <c r="D505" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
@@ -18528,17 +18498,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>110610.jpg</t>
+          <t>110834.jpg</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>110936</v>
+        <v>110307</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH BLACK SURFACE DESIGN 35X28X5CM</t>
+          <t>ACRYLIC BOX WITH 6 PART 35X28X5CM</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -18558,27 +18528,27 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>110936.jpg</t>
+          <t>110307.jpg</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>110933</v>
+        <v>109685</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 27X20X5CM WHITE AND CLEAR</t>
+          <t>BABY BOY FOREX TRAY 30X30X30CM</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Acrylic boxes</t>
+          <t>Forex Stands</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Acrylic</t>
+          <t>Forex</t>
         </is>
       </c>
       <c r="G507" s="18" t="inlineStr">
@@ -18588,27 +18558,27 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>110933.jpg</t>
+          <t>109685.jpg</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>110894</v>
+        <v>105785</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 27X24X5CM</t>
+          <t>BABY BOY TROLLEY CART 52X35X50CM</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Acrylic boxes</t>
+          <t>Forex Stands</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Acrylic</t>
+          <t>Forex</t>
         </is>
       </c>
       <c r="G508" s="18" t="inlineStr">
@@ -18618,27 +18588,27 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>110894.jpg</t>
+          <t>105785.jpg</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>110723</v>
+        <v>109686</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 25X23X11CM</t>
+          <t>BABY BOY TROLLEY FOREX TRAY 33X30C34CM</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Acrylic boxes</t>
+          <t>Forex Stands</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Acrylic</t>
+          <t>Forex</t>
         </is>
       </c>
       <c r="G509" s="18" t="inlineStr">
@@ -18648,27 +18618,27 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>110723.jpg</t>
+          <t>109686.jpg</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>110782</v>
+        <v>115849</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>ACRYLIC NUTS BOX WITH 8 PART 37X19X8CM EMPTY VERSION 2</t>
+          <t>FOREX BABY BLUE WHALE 50X44X25 CM</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Acrylic boxes</t>
+          <t>Forex Stands</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Acrylic</t>
+          <t>Forex</t>
         </is>
       </c>
       <c r="G510" s="18" t="inlineStr">
@@ -18678,27 +18648,27 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>110782.jpg</t>
+          <t>115849.jpg</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>110834</v>
+        <v>115844</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX W/6 PART 35X25X3.5CM</t>
+          <t>FOREX BABY BOY HORSE TOY 55X50X25 CM</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Acrylic boxes</t>
+          <t>Forex Stands</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>Acrylic</t>
+          <t>Forex</t>
         </is>
       </c>
       <c r="G511" s="18" t="inlineStr">
@@ -18708,27 +18678,27 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>110834.jpg</t>
+          <t>115844.jpg</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>110307</v>
+        <v>115847</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH 6 PART 35X28X5CM</t>
+          <t>FOREX BABY BOY W/HAT DESIGN 53X35X25 CM</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Acrylic boxes</t>
+          <t>Forex Stands</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Acrylic</t>
+          <t>Forex</t>
         </is>
       </c>
       <c r="G512" s="18" t="inlineStr">
@@ -18738,17 +18708,17 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>110307.jpg</t>
+          <t>115847.jpg</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>109685</v>
+        <v>115845</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>BABY BOY FOREX TRAY 30X30X30CM</t>
+          <t>FOREX BABY BUTTERFLY DESIGN 57X50X25 CM</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -18768,17 +18738,17 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>109685.jpg</t>
+          <t>115845.jpg</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>105785</v>
+        <v>115914</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>BABY BOY TROLLEY CART 52X35X50CM</t>
+          <t>FOREX BABY CAR W/BALLOON DESIGN 48X25X11 CM</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -18798,17 +18768,17 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>105785.jpg</t>
+          <t>115914.jpg</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>109686</v>
+        <v>115885</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>BABY BOY TROLLEY FOREX TRAY 33X30C34CM</t>
+          <t>FOREX BABY DUCK W/HAT DESIGN 40X40X20 CM</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -18828,17 +18798,17 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>109686.jpg</t>
+          <t>115885.jpg</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>115849</v>
+        <v>115846</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>FOREX BABY BLUE WHALE 50X44X25 CM</t>
+          <t>FOREX BABY DUCK W/HAT DESIGN 68X50X25 CM</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18858,17 +18828,17 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>115849.jpg</t>
+          <t>115846.jpg</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>115844</v>
+        <v>115848</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>FOREX BABY BOY HORSE TOY 55X50X25 CM</t>
+          <t>FOREX BABY GIRL WITH CLIP DESIGN 53X35X25 CM</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18888,17 +18858,17 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>115844.jpg</t>
+          <t>115848.jpg</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>115847</v>
+        <v>115638</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>FOREX BABY BOY W/HAT DESIGN 53X35X25 CM</t>
+          <t>FOREX BABY GIRL ROUND 40CM FLAT WITH HEART 50X37CM</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18918,17 +18888,17 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>115847.jpg</t>
+          <t>115638.jpg</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>115845</v>
+        <v>115883</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>FOREX BABY BUTTERFLY DESIGN 57X50X25 CM</t>
+          <t>FOREX BABY OCTOPUS DESIGN 50X45X25 CM</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18948,17 +18918,17 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>115845.jpg</t>
+          <t>115883.jpg</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>115914</v>
+        <v>115884</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>FOREX BABY CAR W/BALLOON DESIGN 48X25X11 CM</t>
+          <t>FOREX BABY PARACHUTE BALLOON DESIGN 55X45X25 CM</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18978,17 +18948,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>115914.jpg</t>
+          <t>115884.jpg</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>115885</v>
+        <v>115606</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>FOREX BABY DUCK W/HAT DESIGN 40X40X20 CM</t>
+          <t>FOREX BABY TRAY WHITE WITH BLUE FOREX DESIGN 40X32X33X6 CM</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -19008,17 +18978,17 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>115885.jpg</t>
+          <t>115606.jpg</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>115846</v>
+        <v>115621</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>FOREX BABY DUCK W/HAT DESIGN 68X50X25 CM</t>
+          <t>FOREX BABY TRAY WHITE WITH PINK FOREX DESIGN 40X32X33X6 CM</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -19038,17 +19008,17 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>115846.jpg</t>
+          <t>115621.jpg</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>115848</v>
+        <v>110988</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>FOREX BABY GIRL WITH CLIP DESIGN 53X35X25 CM</t>
+          <t>FOREX CAR 55X20X34.6</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -19068,17 +19038,17 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>115848.jpg</t>
+          <t>110988.jpg</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>115638</v>
+        <v>115629</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>FOREX BABY GIRL ROUND 40CM FLAT WITH HEART 50X37CM</t>
+          <t>FOREX DEEP TROLLY BABY BOY 30X25X35 CM</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -19098,17 +19068,17 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>115638.jpg</t>
+          <t>115629.jpg</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>115883</v>
+        <v>115628</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>FOREX BABY OCTOPUS DESIGN 50X45X25 CM</t>
+          <t>FOREX DEEP TROLLY BABY GIRL 30X25X35 CM</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -19128,17 +19098,17 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>115883.jpg</t>
+          <t>115628.jpg</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>115884</v>
+        <v>110354</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>FOREX BABY PARACHUTE BALLOON DESIGN 55X45X25 CM</t>
+          <t>FOREX DUCK TRAY BABY BOY 20X33X36CM</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -19158,17 +19128,17 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>115884.jpg</t>
+          <t>110354.png</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>115606</v>
+        <v>116643</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>FOREX BABY TRAY WHITE WITH BLUE FOREX DESIGN 40X32X33X6 CM</t>
+          <t>FOREX OBLONG TRAY 65x25x5.5CM</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -19188,17 +19158,17 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>115606.jpg</t>
+          <t>116643.jpeg</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>115621</v>
+        <v>110597</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>FOREX BABY TRAY WHITE WITH PINK FOREX DESIGN 40X32X33X6 CM</t>
+          <t>FOREX OBLONG TRAY SMALL 34.5X18X2.5CM</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -19218,17 +19188,17 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>115621.jpg</t>
+          <t>110597.jpg</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>110988</v>
+        <v>116646</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>FOREX CAR 55X20X34.6</t>
+          <t>FOREX OBLONG TRAY W/STICKER 70X40X6 CM</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -19248,17 +19218,17 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>110988.jpg</t>
+          <t>116646.jpeg</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>115629</v>
+        <v>116645</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>FOREX DEEP TROLLY BABY BOY 30X25X35 CM</t>
+          <t>FOREX OBLONG TRAY W/STICKER 70X40X15 CM</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -19278,17 +19248,17 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>115629.jpg</t>
+          <t>116645.jpeg</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>115628</v>
+        <v>116648</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>FOREX DEEP TROLLY BABY GIRL 30X25X35 CM</t>
+          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X6 CM</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -19308,17 +19278,17 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>115628.jpg</t>
+          <t>116648.jpeg</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>110354</v>
+        <v>116647</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>FOREX DUCK TRAY BABY BOY 20X33X36CM</t>
+          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X15 CM</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -19338,17 +19308,17 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>110354.png</t>
+          <t>116647.jpeg</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>116643</v>
+        <v>115916</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY 65x25x5.5CM</t>
+          <t>FOREX OBLONG TROLLEY W/BEE DESIGN 55X30X20 CM</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -19368,17 +19338,17 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>116643.jpeg</t>
+          <t>115916.jpg</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>110597</v>
+        <v>115939</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY SMALL 34.5X18X2.5CM</t>
+          <t>FOREX ROUND TRAY 37X37X5 CM</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -19398,17 +19368,17 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>110597.jpg</t>
+          <t>115939.jpg</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>116646</v>
+        <v>115941</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY W/STICKER 70X40X6 CM</t>
+          <t>FOREX ROUND TRAY 40X40X5 CM</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -19428,17 +19398,17 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>116646.jpeg</t>
+          <t>115941.jpg</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>116645</v>
+        <v>117099</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY W/STICKER 70X40X15 CM</t>
+          <t>FOREX ROUND TRAY 45X45X5 CM</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -19458,17 +19428,17 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>116645.jpeg</t>
+          <t>117099.jpeg</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>116648</v>
+        <v>110924</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X6 CM</t>
+          <t>FOREX SCOOTER BABY GIRL/BOY BIG 55X20X34.6CM</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -19488,17 +19458,17 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>116648.jpeg</t>
+          <t>110924.jpg</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>116647</v>
+        <v>110923</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X15 CM</t>
+          <t>FOREX SCOOTER BABY GIRL/BOY SMALL 40X17X25CM</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -19518,17 +19488,17 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>116647.jpeg</t>
+          <t>110923.jpg</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>115916</v>
+        <v>115639</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TROLLEY W/BEE DESIGN 55X30X20 CM</t>
+          <t>FOREX STAND BABY BEAR 75X35X15 CM</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -19548,17 +19518,17 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>115916.jpg</t>
+          <t>115639.jpg</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>115939</v>
+        <v>115627</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>FOREX ROUND TRAY 37X37X5 CM</t>
+          <t>FOREX STAND BABY BOY 2 LAYERS 43X31CM 31X31CM H70 CM</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -19578,17 +19548,17 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>115939.jpg</t>
+          <t>115627.jpg</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>115941</v>
+        <v>115626</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>FOREX ROUND TRAY 40X40X5 CM</t>
+          <t>FOREX STAND BABY GIRL 2 LAYERS 43X31CM 31X31CM H70 CM</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -19608,17 +19578,17 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>115941.jpg</t>
+          <t>115626.jpg</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>117099</v>
+        <v>112892</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>FOREX ROUND TRAY 45X45X5 CM</t>
+          <t>FOREX TRAY 20X17X15CM</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -19638,17 +19608,17 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>117099.jpeg</t>
+          <t>112892.jpg</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>110924</v>
+        <v>115002</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>FOREX SCOOTER BABY GIRL/BOY BIG 55X20X34.6CM</t>
+          <t>FOREX TRAY BABY BOY 41X39X4CM</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -19668,17 +19638,17 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>110924.jpg</t>
+          <t>115002.jpg</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>110923</v>
+        <v>115001</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>FOREX SCOOTER BABY GIRL/BOY SMALL 40X17X25CM</t>
+          <t>FOREX TRAY BABY GIRL 31X29X4CM</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -19698,17 +19668,17 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>110923.jpg</t>
+          <t>115001.jpg</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>115639</v>
+        <v>114999</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>FOREX STAND BABY BEAR 75X35X15 CM</t>
+          <t>FOREX TRAY BABY GIRL 41X39X4CM</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -19728,17 +19698,17 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>115639.jpg</t>
+          <t>114999.jpg</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>115627</v>
+        <v>115003</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>FOREX STAND BABY BOY 2 LAYERS 43X31CM 31X31CM H70 CM</t>
+          <t>FOREX TRAY BABY GIRL LADDER AND RIBBON 41X39X39CM</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -19758,17 +19728,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>115627.jpg</t>
+          <t>115003.jpg</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>115626</v>
+        <v>115635</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>FOREX STAND BABY GIRL 2 LAYERS 43X31CM 31X31CM H70 CM</t>
+          <t>FOREX TRAY BOY 30X30X4CM BOARD 28CM</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -19788,17 +19758,17 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>115626.jpg</t>
+          <t>115635.jpg</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>112892</v>
+        <v>115623</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>FOREX TRAY 20X17X15CM</t>
+          <t>FOREX TRAY GIRL 30X30X4CM BOARD 28CM</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -19818,17 +19788,17 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>112892.jpg</t>
+          <t>115632.jpg</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>115002</v>
+        <v>115630</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY BOY 41X39X4CM</t>
+          <t>FOREX TRAY GIRL BOY 30X30X4CM BOARD 20CM</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -19848,17 +19818,17 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>115002.jpg</t>
+          <t>115630.jpg</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>115001</v>
+        <v>112889</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY GIRL 31X29X4CM</t>
+          <t>FOREX TV 25X20X22.5CM</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -19878,17 +19848,17 @@
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>115001.jpg</t>
+          <t>112889.jpg</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>114999</v>
+        <v>115858</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY GIRL 41X39X4CM</t>
+          <t>FOREX W/ACRYLIC OBLONG TRAY 70X40X15 CM</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -19908,17 +19878,17 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>114999.jpg</t>
+          <t>115858.jpg</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>115003</v>
+        <v>110502</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY GIRL LADDER AND RIBBON 41X39X39CM</t>
+          <t>FOREX WRINTING STAND 25X15CM</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -19938,17 +19908,17 @@
       </c>
       <c r="I552" t="inlineStr">
         <is>
-          <t>115003.jpg</t>
+          <t>110502.jpg</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>115635</v>
+        <v>110598</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>FOREX TRAY BOY 30X30X4CM BOARD 28CM</t>
+          <t>FOREX OBLONG TRAY MEDIUM 40X21X2.5CM</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -19964,21 +19934,16 @@
       <c r="G553" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
-        </is>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>115635.jpg</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>115623</v>
+        <v>110599</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>FOREX TRAY GIRL 30X30X4CM BOARD 28CM</t>
+          <t>FOREX OBLONG TRAY LARGE 45X23.5X2.5CM</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -19994,21 +19959,16 @@
       <c r="G554" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
-        </is>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>115632.jpg</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>115630</v>
+        <v>104760</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>FOREX TRAY GIRL BOY 30X30X4CM BOARD 20CM</t>
+          <t>FLAT FOREX WHITE 29.729.71CM</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -20028,17 +19988,17 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>115630.jpg</t>
+          <t>104760.png</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>112889</v>
+        <v>104761</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>FOREX TV 25X20X22.5CM</t>
+          <t>FLAT FOREX WHITE 35.35.1CM</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -20058,17 +20018,17 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>112889.jpg</t>
+          <t>104761.PNG</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>115858</v>
+        <v>104762</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>FOREX W/ACRYLIC OBLONG TRAY 70X40X15 CM</t>
+          <t>FLAT FOREX WHITE 39.739.71CM</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -20088,17 +20048,17 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>115858.jpg</t>
+          <t>104762.png</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>110502</v>
+        <v>104763</v>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>FOREX WRINTING STAND 25X15CM</t>
+          <t>FLAT FOREX WHITE 49.749.71CM</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -20114,21 +20074,16 @@
       <c r="G558" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>110502.jpg</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>110598</v>
+        <v>109676</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY MEDIUM 40X21X2.5CM</t>
+          <t>FOREX BABY BOY CAR 40X22X18CM</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -20146,24 +20101,31 @@
           <t>PCS</t>
         </is>
       </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>109676.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="560">
-      <c r="A560" t="n">
-        <v>110599</v>
+      <c r="A560" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">117632 </t>
+        </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY LARGE 45X23.5X2.5CM</t>
+          <t>Premium Wafer Cerelak JAR</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Forex Stands</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>Forex</t>
+          <t>Wafer</t>
+        </is>
+      </c>
+      <c r="D560" s="15" t="inlineStr">
+        <is>
+          <t>Jars</t>
         </is>
       </c>
       <c r="G560" s="18" t="inlineStr">
@@ -20174,198 +20136,26 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>104760</v>
+        <v>107840</v>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>FLAT FOREX WHITE 29.729.71CM</t>
+          <t>Dragee box mix</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Forex Stands</t>
+          <t>Special</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Forex</t>
-        </is>
-      </c>
-      <c r="G561" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="I561" t="inlineStr">
-        <is>
-          <t>104760.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="n">
-        <v>104761</v>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>FLAT FOREX WHITE 35.35.1CM</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>Forex Stands</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>Forex</t>
-        </is>
-      </c>
-      <c r="G562" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>104761.PNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="n">
-        <v>104762</v>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>FLAT FOREX WHITE 39.739.71CM</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>Forex Stands</t>
-        </is>
-      </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>Forex</t>
-        </is>
-      </c>
-      <c r="G563" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="I563" t="inlineStr">
-        <is>
-          <t>104762.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="n">
-        <v>104763</v>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>FLAT FOREX WHITE 49.749.71CM</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>Forex Stands</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>Forex</t>
-        </is>
-      </c>
-      <c r="G564" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="n">
-        <v>109676</v>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>FOREX BABY BOY CAR 40X22X18CM</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>Forex Stands</t>
-        </is>
-      </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>Forex</t>
-        </is>
-      </c>
-      <c r="G565" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
-          <t>109676.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117632 </t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>Premium Wafer Cerelak JAR</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>Wafer</t>
-        </is>
-      </c>
-      <c r="D566" s="15" t="inlineStr">
-        <is>
-          <t>Jars</t>
-        </is>
-      </c>
-      <c r="G566" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="n">
-        <v>107840</v>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>Dragee box mix</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="D567" t="inlineStr">
-        <is>
           <t>Secondary items</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I468"/>
+  <autoFilter ref="A1:I462"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -4425,7 +4425,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>112664.jpg</t>
+          <t>custom-mini-extra.jpg</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16284,11 @@
       <c r="H437" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="I437" s="2" t="n"/>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>custom-custmoized-egg.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -16983,7 +16987,11 @@
       <c r="H456" s="3" t="n">
         <v>141.75</v>
       </c>
-      <c r="I456" s="2" t="n"/>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>custom-wrapped-belgium-baby-boy-mix.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -17016,7 +17024,11 @@
       <c r="H457" s="3" t="n">
         <v>141.75</v>
       </c>
-      <c r="I457" s="2" t="n"/>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>custom-wrapped-belgium-baby-boy-slice-dirham.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -17049,7 +17061,11 @@
       <c r="H458" s="3" t="n">
         <v>141.75</v>
       </c>
-      <c r="I458" s="2" t="n"/>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>custom-wrapped-belgium-baby-girl-mix.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -17082,7 +17098,11 @@
       <c r="H459" s="3" t="n">
         <v>141.75</v>
       </c>
-      <c r="I459" s="2" t="n"/>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>custom-wrapped-belgium-baby-girl-slice-dirham.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -17115,7 +17135,11 @@
       <c r="H460" s="3" t="n">
         <v>141.75</v>
       </c>
-      <c r="I460" s="2" t="n"/>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>custom-big-sequare-belgium-wrapped.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="15" t="inlineStr">
@@ -20131,6 +20155,11 @@
       <c r="G560" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>custom-premium-wafer-cerelak-jar.jpg</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I565"/>
+  <dimension ref="A1:I566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>custom-wrapped-belgium-gold-mix.jpg</t>
+          <t>custom-wrapped-belgium-gold-mix-v2.jpg</t>
         </is>
       </c>
     </row>
@@ -16884,24 +16884,24 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>108656.jpg</t>
+          <t>custom-belgium-square-wafer-with-chocolate-print-kg.jpg</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>100382</t>
+          <t>100384</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>Wrapped Belgium Baby Boy mix</t>
+          <t>Square wafer with paper print</t>
         </is>
       </c>
       <c r="C454" s="15" t="inlineStr">
         <is>
-          <t>Belgium wrapped</t>
+          <t>Customized</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -16916,12 +16916,10 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="H454" s="3" t="n">
-        <v>141.75</v>
-      </c>
+      <c r="H454" s="3" t="n"/>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>custom-wrapped-belgium-baby-boy-mix.jpg</t>
+          <t>custom-square-wafer-with-paper-print.jpg</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16931,7 @@
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>Wrapped Belgium Baby Boy Slice Dirham</t>
+          <t>Wrapped Belgium Baby Boy mix</t>
         </is>
       </c>
       <c r="C455" s="15" t="inlineStr">
@@ -16958,7 +16956,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>custom-wrapped-belgium-baby-boy-slice-dirham.jpg</t>
+          <t>custom-wrapped-belgium-baby-boy-mix.jpg</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16968,7 @@
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>Wrapped Belgium Baby Girl mix</t>
+          <t>Wrapped Belgium Baby Boy Slice Dirham</t>
         </is>
       </c>
       <c r="C456" s="15" t="inlineStr">
@@ -16995,7 +16993,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>custom-wrapped-belgium-baby-girl-mix.jpg</t>
+          <t>custom-wrapped-belgium-baby-boy-slice-dirham.jpg</t>
         </is>
       </c>
     </row>
@@ -17007,7 +17005,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>Wrapped Belgium Baby Girl Slice Dirham</t>
+          <t>Wrapped Belgium Baby Girl mix</t>
         </is>
       </c>
       <c r="C457" s="15" t="inlineStr">
@@ -17032,7 +17030,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>custom-wrapped-belgium-baby-girl-slice-dirham.jpg</t>
+          <t>custom-wrapped-belgium-baby-girl-mix.jpg</t>
         </is>
       </c>
     </row>
@@ -17044,7 +17042,7 @@
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>Big Sequare Belgium wrapped</t>
+          <t>Wrapped Belgium Baby Girl Slice Dirham</t>
         </is>
       </c>
       <c r="C458" s="15" t="inlineStr">
@@ -17069,29 +17067,29 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>custom-big-sequare-belgium-wrapped.jpg</t>
+          <t>custom-wrapped-belgium-baby-girl-slice-dirham.jpg</t>
         </is>
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="15" t="inlineStr">
-        <is>
-          <t>106191</t>
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>100382</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>Premium apricoat with almond kg</t>
+          <t>Big Sequare Belgium wrapped</t>
         </is>
       </c>
       <c r="C459" s="15" t="inlineStr">
         <is>
-          <t>Apricoat</t>
-        </is>
-      </c>
-      <c r="D459" s="15" t="inlineStr">
-        <is>
-          <t>Dry fruit</t>
+          <t>Belgium wrapped</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Belgium chocolate</t>
         </is>
       </c>
       <c r="E459" s="2" t="n"/>
@@ -17102,11 +17100,11 @@
         </is>
       </c>
       <c r="H459" s="3" t="n">
-        <v>147</v>
+        <v>141.75</v>
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>111221.jpg</t>
+          <t>custom-big-sequare-belgium-wrapped.jpg</t>
         </is>
       </c>
     </row>
@@ -17118,7 +17116,7 @@
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>Premium apricoat with cashew kg</t>
+          <t>Premium apricoat with almond kg</t>
         </is>
       </c>
       <c r="C460" s="15" t="inlineStr">
@@ -17143,7 +17141,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>111252.jpg</t>
+          <t>111221.jpg</t>
         </is>
       </c>
     </row>
@@ -17153,9 +17151,9 @@
           <t>106191</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>Premium apricoat with hazelnut kg</t>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>Premium apricoat with cashew kg</t>
         </is>
       </c>
       <c r="C461" s="15" t="inlineStr">
@@ -17180,7 +17178,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>111253.jpg</t>
+          <t>111252.jpg</t>
         </is>
       </c>
     </row>
@@ -17192,7 +17190,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Premium apricoat with walnut kg</t>
+          <t>Premium apricoat with hazelnut kg</t>
         </is>
       </c>
       <c r="C462" s="15" t="inlineStr">
@@ -17217,7 +17215,7 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>111255.jpg</t>
+          <t>111253.jpg</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17227,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Premium apricoat with white walnut kg</t>
+          <t>Premium apricoat with walnut kg</t>
         </is>
       </c>
       <c r="C463" s="15" t="inlineStr">
@@ -17254,47 +17252,54 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
+          <t>111255.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" customFormat="1" s="18">
+      <c r="A464" s="15" t="inlineStr">
+        <is>
+          <t>106191</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Premium apricoat with white walnut kg</t>
+        </is>
+      </c>
+      <c r="C464" s="15" t="inlineStr">
+        <is>
+          <t>Apricoat</t>
+        </is>
+      </c>
+      <c r="D464" s="15" t="inlineStr">
+        <is>
+          <t>Dry fruit</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="n"/>
+      <c r="F464" s="2" t="n"/>
+      <c r="G464" s="8" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="H464" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
           <t>115250.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="464" customFormat="1" s="18">
-      <c r="A464" s="18" t="n">
-        <v>110486</v>
-      </c>
-      <c r="B464" s="18" t="inlineStr">
-        <is>
-          <t>ACRYLC BOX 30X25X12 CM WITH PAPER HOLDER</t>
-        </is>
-      </c>
-      <c r="C464" s="18" t="inlineStr">
-        <is>
-          <t>Acrylic boxes</t>
-        </is>
-      </c>
-      <c r="D464" s="18" t="inlineStr">
-        <is>
-          <t>Acrylic</t>
-        </is>
-      </c>
-      <c r="G464" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="I464" t="inlineStr">
-        <is>
-          <t>110486.jpg</t>
         </is>
       </c>
     </row>
     <row r="465" customFormat="1" s="18">
       <c r="A465" s="18" t="n">
-        <v>110487</v>
+        <v>110486</v>
       </c>
       <c r="B465" s="18" t="inlineStr">
         <is>
-          <t>ACRYLC BOX 30X25X7 CM WITH PAPER HOLDER</t>
+          <t>ACRYLC BOX 30X25X12 CM WITH PAPER HOLDER</t>
         </is>
       </c>
       <c r="C465" s="18" t="inlineStr">
@@ -17314,17 +17319,17 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>110487.jpg</t>
+          <t>110486.jpg</t>
         </is>
       </c>
     </row>
     <row r="466" customFormat="1" s="18">
       <c r="A466" s="18" t="n">
-        <v>109806</v>
+        <v>110487</v>
       </c>
       <c r="B466" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY SMALL 32.5X20X4CM</t>
+          <t>ACRYLC BOX 30X25X7 CM WITH PAPER HOLDER</t>
         </is>
       </c>
       <c r="C466" s="18" t="inlineStr">
@@ -17344,17 +17349,17 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>109806.jpg</t>
+          <t>110487.jpg</t>
         </is>
       </c>
     </row>
     <row r="467" customFormat="1" s="18">
       <c r="A467" s="18" t="n">
-        <v>109807</v>
+        <v>109806</v>
       </c>
       <c r="B467" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY MEDIUM 36.3X22.7X4.5CM</t>
+          <t>ACRYLIC TRAY SMALL 32.5X20X4CM</t>
         </is>
       </c>
       <c r="C467" s="18" t="inlineStr">
@@ -17374,17 +17379,17 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>109807.jpg</t>
+          <t>109806.jpg</t>
         </is>
       </c>
     </row>
     <row r="468" customFormat="1" s="18">
       <c r="A468" s="18" t="n">
-        <v>107808</v>
+        <v>109807</v>
       </c>
       <c r="B468" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY LARGE 40X25X5CM</t>
+          <t>ACRYLIC TRAY MEDIUM 36.3X22.7X4.5CM</t>
         </is>
       </c>
       <c r="C468" s="18" t="inlineStr">
@@ -17404,17 +17409,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>109808.jpg</t>
+          <t>109807.jpg</t>
         </is>
       </c>
     </row>
     <row r="469" customFormat="1" s="18">
       <c r="A469" s="18" t="n">
-        <v>110483</v>
+        <v>107808</v>
       </c>
       <c r="B469" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 18X15X4.5CM</t>
+          <t>ACRYLIC TRAY LARGE 40X25X5CM</t>
         </is>
       </c>
       <c r="C469" s="18" t="inlineStr">
@@ -17434,17 +17439,17 @@
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>110483.jpg</t>
+          <t>109808.jpg</t>
         </is>
       </c>
     </row>
     <row r="470" customFormat="1" s="18">
       <c r="A470" s="18" t="n">
-        <v>108081</v>
+        <v>110483</v>
       </c>
       <c r="B470" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 23X50X11 WITH PARTITION EMPTY</t>
+          <t>ACRYLIC BOX 18X15X4.5CM</t>
         </is>
       </c>
       <c r="C470" s="18" t="inlineStr">
@@ -17464,17 +17469,17 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>108081.jpg</t>
+          <t>110483.jpg</t>
         </is>
       </c>
     </row>
     <row r="471" customFormat="1" s="18">
       <c r="A471" s="18" t="n">
-        <v>110608</v>
+        <v>108081</v>
       </c>
       <c r="B471" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 30X8X6CM</t>
+          <t>ACRYLIC BOX 23X50X11 WITH PARTITION EMPTY</t>
         </is>
       </c>
       <c r="C471" s="18" t="inlineStr">
@@ -17494,17 +17499,17 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>110608.jpg</t>
+          <t>108081.jpg</t>
         </is>
       </c>
     </row>
     <row r="472" customFormat="1" s="18">
       <c r="A472" s="18" t="n">
-        <v>109042</v>
+        <v>110608</v>
       </c>
       <c r="B472" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH ACRYLIC GOLD DESIGN IN COVER 21X14X4CM</t>
+          <t>ACRYLIC BOX 30X8X6CM</t>
         </is>
       </c>
       <c r="C472" s="18" t="inlineStr">
@@ -17524,17 +17529,17 @@
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>109042.jpg</t>
+          <t>110608.jpg</t>
         </is>
       </c>
     </row>
     <row r="473" customFormat="1" s="18">
       <c r="A473" s="18" t="n">
-        <v>110509</v>
+        <v>109042</v>
       </c>
       <c r="B473" s="18" t="inlineStr">
         <is>
-          <t>FOREX AND ACRYLIC BOX 57X27X3CM</t>
+          <t>ACRYLIC BOX WITH ACRYLIC GOLD DESIGN IN COVER 21X14X4CM</t>
         </is>
       </c>
       <c r="C473" s="18" t="inlineStr">
@@ -17554,17 +17559,17 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>110509.jpg</t>
+          <t>109042.jpg</t>
         </is>
       </c>
     </row>
     <row r="474" customFormat="1" s="18">
       <c r="A474" s="18" t="n">
-        <v>109044</v>
+        <v>110509</v>
       </c>
       <c r="B474" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH CHAIN HANDLE 21X10X16 CM EMPTY</t>
+          <t>FOREX AND ACRYLIC BOX 57X27X3CM</t>
         </is>
       </c>
       <c r="C474" s="18" t="inlineStr">
@@ -17584,17 +17589,17 @@
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>109044.jpg</t>
+          <t>110509.jpg</t>
         </is>
       </c>
     </row>
     <row r="475" customFormat="1" s="18">
       <c r="A475" s="18" t="n">
-        <v>108972</v>
+        <v>109044</v>
       </c>
       <c r="B475" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH CHAIN HANDLE</t>
+          <t>ACRYLIC BOX WITH CHAIN HANDLE 21X10X16 CM EMPTY</t>
         </is>
       </c>
       <c r="C475" s="18" t="inlineStr">
@@ -17614,17 +17619,17 @@
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>108972.jpg</t>
+          <t>109044.jpg</t>
         </is>
       </c>
     </row>
     <row r="476" customFormat="1" s="18">
       <c r="A476" s="18" t="n">
-        <v>110045</v>
+        <v>108972</v>
       </c>
       <c r="B476" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC TRAY CHOCOLALA 40X20X34CM</t>
+          <t>ACRYLIC BOX WITH CHAIN HANDLE</t>
         </is>
       </c>
       <c r="C476" s="18" t="inlineStr">
@@ -17644,17 +17649,17 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>110045.jpg</t>
+          <t>108972.jpg</t>
         </is>
       </c>
     </row>
     <row r="477" customFormat="1" s="18">
       <c r="A477" s="18" t="n">
-        <v>110047</v>
+        <v>110045</v>
       </c>
       <c r="B477" s="18" t="inlineStr">
         <is>
-          <t>GOLD RECTANGLE HANDLE ACRYLIC BOX (30X20X30CM)</t>
+          <t>ACRYLIC TRAY CHOCOLALA 40X20X34CM</t>
         </is>
       </c>
       <c r="C477" s="18" t="inlineStr">
@@ -17674,17 +17679,17 @@
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>110047.jpg</t>
+          <t>110045.jpg</t>
         </is>
       </c>
     </row>
     <row r="478" customFormat="1" s="18">
       <c r="A478" s="18" t="n">
-        <v>110046</v>
+        <v>110047</v>
       </c>
       <c r="B478" s="18" t="inlineStr">
         <is>
-          <t>GOLD HEART HANDLE ACRYLIC BAG-BOX (30X20X39.5)</t>
+          <t>GOLD RECTANGLE HANDLE ACRYLIC BOX (30X20X30CM)</t>
         </is>
       </c>
       <c r="C478" s="18" t="inlineStr">
@@ -17704,17 +17709,17 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>110046.jpg</t>
+          <t>110047.jpg</t>
         </is>
       </c>
     </row>
     <row r="479" customFormat="1" s="18">
       <c r="A479" s="18" t="n">
-        <v>110723</v>
+        <v>110046</v>
       </c>
       <c r="B479" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 25X23X11CM</t>
+          <t>GOLD HEART HANDLE ACRYLIC BAG-BOX (30X20X39.5)</t>
         </is>
       </c>
       <c r="C479" s="18" t="inlineStr">
@@ -17734,17 +17739,17 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>110723.jpg</t>
+          <t>110046.jpg</t>
         </is>
       </c>
     </row>
     <row r="480" customFormat="1" s="18">
       <c r="A480" s="18" t="n">
-        <v>109862</v>
+        <v>110723</v>
       </c>
       <c r="B480" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH PARTITION 42.5X16X3.5CM</t>
+          <t>ACRYLIC BOX 25X23X11CM</t>
         </is>
       </c>
       <c r="C480" s="18" t="inlineStr">
@@ -17764,17 +17769,17 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>109862.jpg</t>
+          <t>110723.jpg</t>
         </is>
       </c>
     </row>
     <row r="481" customFormat="1" s="18">
       <c r="A481" s="18" t="n">
-        <v>110321</v>
+        <v>109862</v>
       </c>
       <c r="B481" s="18" t="inlineStr">
         <is>
-          <t>CHOCOLA PURE ACRYLIC BOX W 9 PARTITION 90X39X5CM</t>
+          <t>ACRYLIC BOX WITH PARTITION 42.5X16X3.5CM</t>
         </is>
       </c>
       <c r="C481" s="18" t="inlineStr">
@@ -17794,17 +17799,17 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>110321.jpg</t>
+          <t>109862.jpg</t>
         </is>
       </c>
     </row>
     <row r="482" customFormat="1" s="18">
       <c r="A482" s="18" t="n">
-        <v>110435</v>
+        <v>110321</v>
       </c>
       <c r="B482" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 16X16X4CM</t>
+          <t>CHOCOLA PURE ACRYLIC BOX W 9 PARTITION 90X39X5CM</t>
         </is>
       </c>
       <c r="C482" s="18" t="inlineStr">
@@ -17824,17 +17829,17 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>110435.jpg</t>
+          <t>110321.jpg</t>
         </is>
       </c>
     </row>
     <row r="483" customFormat="1" s="18">
       <c r="A483" s="18" t="n">
-        <v>110660</v>
+        <v>110435</v>
       </c>
       <c r="B483" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 30X16.5X9CM 20 PART. W/ CHOCO BOARD</t>
+          <t>ACRYLIC BOX 16X16X4CM</t>
         </is>
       </c>
       <c r="C483" s="18" t="inlineStr">
@@ -17854,17 +17859,17 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>110660.jpg</t>
+          <t>110435.jpg</t>
         </is>
       </c>
     </row>
     <row r="484" customFormat="1" s="18">
       <c r="A484" s="18" t="n">
-        <v>110436</v>
+        <v>110660</v>
       </c>
       <c r="B484" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 26X18X6CM</t>
+          <t>ACRYLIC BOX 30X16.5X9CM 20 PART. W/ CHOCO BOARD</t>
         </is>
       </c>
       <c r="C484" s="18" t="inlineStr">
@@ -17884,17 +17889,17 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>110436.jpg</t>
+          <t>110660.jpg</t>
         </is>
       </c>
     </row>
     <row r="485" customFormat="1" s="18">
       <c r="A485" s="18" t="n">
-        <v>108954</v>
+        <v>110436</v>
       </c>
       <c r="B485" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 35X28X5CM</t>
+          <t>ACRYLIC BOX 26X18X6CM</t>
         </is>
       </c>
       <c r="C485" s="18" t="inlineStr">
@@ -17914,17 +17919,17 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>108954.jpg</t>
+          <t>110436.jpg</t>
         </is>
       </c>
     </row>
     <row r="486" customFormat="1" s="18">
       <c r="A486" s="18" t="n">
-        <v>110434</v>
+        <v>108954</v>
       </c>
       <c r="B486" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX CLEAR 28X25X5CM EMPTY</t>
+          <t>ACRYLIC BOX 35X28X5CM</t>
         </is>
       </c>
       <c r="C486" s="18" t="inlineStr">
@@ -17944,17 +17949,17 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>110434.jpg</t>
+          <t>108954.jpg</t>
         </is>
       </c>
     </row>
     <row r="487" customFormat="1" s="18">
       <c r="A487" s="18" t="n">
-        <v>100674</v>
+        <v>110434</v>
       </c>
       <c r="B487" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOXES CLEAR W/ COLORED BASE EMPTY</t>
+          <t>ACRYLIC BOX CLEAR 28X25X5CM EMPTY</t>
         </is>
       </c>
       <c r="C487" s="18" t="inlineStr">
@@ -17974,17 +17979,17 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>100674.PNG</t>
+          <t>110434.jpg</t>
         </is>
       </c>
     </row>
     <row r="488" customFormat="1" s="18">
       <c r="A488" s="18" t="n">
-        <v>110301</v>
+        <v>100674</v>
       </c>
       <c r="B488" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 21X21X5CM</t>
+          <t>ACRYLIC BOXES CLEAR W/ COLORED BASE EMPTY</t>
         </is>
       </c>
       <c r="C488" s="18" t="inlineStr">
@@ -18004,17 +18009,17 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>110301.jpg</t>
+          <t>100674.PNG</t>
         </is>
       </c>
     </row>
     <row r="489" customFormat="1" s="18">
       <c r="A489" s="18" t="n">
-        <v>110007</v>
+        <v>110301</v>
       </c>
       <c r="B489" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 50x20x5CM WHITE EMPTY</t>
+          <t>ACRYLIC BOX 21X21X5CM</t>
         </is>
       </c>
       <c r="C489" s="18" t="inlineStr">
@@ -18034,17 +18039,17 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>110007.jpg</t>
+          <t>110301.jpg</t>
         </is>
       </c>
     </row>
     <row r="490" customFormat="1" s="18">
       <c r="A490" s="18" t="n">
-        <v>108658</v>
+        <v>110007</v>
       </c>
       <c r="B490" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 60x21x4cm</t>
+          <t>ACRYLIC BOX 50x20x5CM WHITE EMPTY</t>
         </is>
       </c>
       <c r="C490" s="18" t="inlineStr">
@@ -18064,17 +18069,17 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>112420.jpg</t>
+          <t>110007.jpg</t>
         </is>
       </c>
     </row>
     <row r="491" customFormat="1" s="18">
       <c r="A491" s="18" t="n">
-        <v>108383</v>
+        <v>108658</v>
       </c>
       <c r="B491" s="18" t="inlineStr">
         <is>
-          <t>HEXAGON DESIGN ACRYLIC BOX SMALL 30*26*5CM EMPTY</t>
+          <t>ACRYLIC BOX 60x21x4cm</t>
         </is>
       </c>
       <c r="C491" s="18" t="inlineStr">
@@ -18094,17 +18099,17 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>108383.jpg</t>
+          <t>112420.jpg</t>
         </is>
       </c>
     </row>
     <row r="492" customFormat="1" s="18">
       <c r="A492" s="18" t="n">
-        <v>108385</v>
+        <v>108383</v>
       </c>
       <c r="B492" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH STAND MEDIUM 40.5*35*5 CM EMPTY</t>
+          <t>HEXAGON DESIGN ACRYLIC BOX SMALL 30*26*5CM EMPTY</t>
         </is>
       </c>
       <c r="C492" s="18" t="inlineStr">
@@ -18124,17 +18129,17 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>108385.jpg</t>
+          <t>108383.jpg</t>
         </is>
       </c>
     </row>
     <row r="493" customFormat="1" s="18">
       <c r="A493" s="18" t="n">
-        <v>108386</v>
+        <v>108385</v>
       </c>
       <c r="B493" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH STAND LARGE 51.5*44.5*5CM</t>
+          <t>ACRYLIC BOX WITH STAND MEDIUM 40.5*35*5 CM EMPTY</t>
         </is>
       </c>
       <c r="C493" s="18" t="inlineStr">
@@ -18154,17 +18159,17 @@
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>108386.jpg</t>
+          <t>108385.jpg</t>
         </is>
       </c>
     </row>
     <row r="494" customFormat="1" s="18">
       <c r="A494" s="18" t="n">
-        <v>105755</v>
+        <v>108386</v>
       </c>
       <c r="B494" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC DRAGEEE BOX EMPTY</t>
+          <t>ACRYLIC BOX WITH STAND LARGE 51.5*44.5*5CM</t>
         </is>
       </c>
       <c r="C494" s="18" t="inlineStr">
@@ -18184,17 +18189,17 @@
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>105755.jpg</t>
+          <t>108386.jpg</t>
         </is>
       </c>
     </row>
     <row r="495" customFormat="1" s="18">
       <c r="A495" s="18" t="n">
-        <v>100678</v>
+        <v>105755</v>
       </c>
       <c r="B495" s="18" t="inlineStr">
         <is>
-          <t>CHOCOLALA RECT. ACRYLIC BOX 23X78X6 EMPTY</t>
+          <t>ACRYLIC DRAGEEE BOX EMPTY</t>
         </is>
       </c>
       <c r="C495" s="18" t="inlineStr">
@@ -18214,17 +18219,17 @@
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>100678.png</t>
+          <t>105755.jpg</t>
         </is>
       </c>
     </row>
     <row r="496" customFormat="1" s="18">
       <c r="A496" s="18" t="n">
-        <v>107554</v>
+        <v>100678</v>
       </c>
       <c r="B496" s="18" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 50*23*11CM (EMPTY)</t>
+          <t>CHOCOLALA RECT. ACRYLIC BOX 23X78X6 EMPTY</t>
         </is>
       </c>
       <c r="C496" s="18" t="inlineStr">
@@ -18244,77 +18249,77 @@
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>107554.jpg</t>
+          <t>100678.png</t>
         </is>
       </c>
     </row>
     <row r="497" customFormat="1" s="18">
       <c r="A497" s="18" t="n">
+        <v>107554</v>
+      </c>
+      <c r="B497" s="18" t="inlineStr">
+        <is>
+          <t>ACRYLIC BOX 50*23*11CM (EMPTY)</t>
+        </is>
+      </c>
+      <c r="C497" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic boxes</t>
+        </is>
+      </c>
+      <c r="D497" s="18" t="inlineStr">
+        <is>
+          <t>Acrylic</t>
+        </is>
+      </c>
+      <c r="G497" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>107554.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="18" t="n">
         <v>110610</v>
       </c>
-      <c r="B497" s="18" t="inlineStr">
+      <c r="B498" s="18" t="inlineStr">
         <is>
           <t>ACRYLIC BOX BUTTERFLY STAND 40X16X16CM</t>
         </is>
       </c>
-      <c r="C497" s="18" t="inlineStr">
+      <c r="C498" s="18" t="inlineStr">
         <is>
           <t>Acrylic boxes</t>
         </is>
       </c>
-      <c r="D497" s="18" t="inlineStr">
+      <c r="D498" s="18" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
       </c>
-      <c r="G497" s="18" t="inlineStr">
+      <c r="G498" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="I497" t="inlineStr">
+      <c r="I498" t="inlineStr">
         <is>
           <t>110610.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="n">
-        <v>110936</v>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>ACRYLIC BOX WITH BLACK SURFACE DESIGN 35X28X5CM</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Acrylic boxes</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>Acrylic</t>
-        </is>
-      </c>
-      <c r="G498" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
-      <c r="I498" t="inlineStr">
-        <is>
-          <t>110936.jpg</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>110933</v>
+        <v>110936</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 27X20X5CM WHITE AND CLEAR</t>
+          <t>ACRYLIC BOX WITH BLACK SURFACE DESIGN 35X28X5CM</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -18334,17 +18339,17 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>110933.jpg</t>
+          <t>110936.jpg</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>110894</v>
+        <v>110933</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 27X24X5CM</t>
+          <t>ACRYLIC BOX 27X20X5CM WHITE AND CLEAR</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -18364,17 +18369,17 @@
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>110894.jpg</t>
+          <t>110933.jpg</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>110723</v>
+        <v>110894</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX 25X23X11CM</t>
+          <t>ACRYLIC BOX 27X24X5CM</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -18394,17 +18399,17 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>110723.jpg</t>
+          <t>110894.jpg</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>110782</v>
+        <v>110723</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>ACRYLIC NUTS BOX WITH 8 PART 37X19X8CM EMPTY VERSION 2</t>
+          <t>ACRYLIC BOX 25X23X11CM</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -18424,17 +18429,17 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>110782.jpg</t>
+          <t>110723.jpg</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>110834</v>
+        <v>110782</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX W/6 PART 35X25X3.5CM</t>
+          <t>ACRYLIC NUTS BOX WITH 8 PART 37X19X8CM EMPTY VERSION 2</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -18454,17 +18459,17 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>110834.jpg</t>
+          <t>110782.jpg</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>110307</v>
+        <v>110834</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>ACRYLIC BOX WITH 6 PART 35X28X5CM</t>
+          <t>ACRYLIC BOX W/6 PART 35X25X3.5CM</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -18484,27 +18489,27 @@
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>110307.jpg</t>
+          <t>110834.jpg</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>109685</v>
+        <v>110307</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>BABY BOY FOREX TRAY 30X30X30CM</t>
+          <t>ACRYLIC BOX WITH 6 PART 35X28X5CM</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Forex Stands</t>
+          <t>Acrylic boxes</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Forex</t>
+          <t>Acrylic</t>
         </is>
       </c>
       <c r="G505" s="18" t="inlineStr">
@@ -18514,17 +18519,17 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>109685.jpg</t>
+          <t>110307.jpg</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>105785</v>
+        <v>109685</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>BABY BOY TROLLEY CART 52X35X50CM</t>
+          <t>BABY BOY FOREX TRAY 30X30X30CM</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -18544,17 +18549,17 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>105785.jpg</t>
+          <t>109685.jpg</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>109686</v>
+        <v>105785</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>BABY BOY TROLLEY FOREX TRAY 33X30C34CM</t>
+          <t>BABY BOY TROLLEY CART 52X35X50CM</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -18574,17 +18579,17 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>109686.jpg</t>
+          <t>105785.jpg</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>115849</v>
+        <v>109686</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>FOREX BABY BLUE WHALE 50X44X25 CM</t>
+          <t>BABY BOY TROLLEY FOREX TRAY 33X30C34CM</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -18604,17 +18609,17 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>115849.jpg</t>
+          <t>109686.jpg</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>115844</v>
+        <v>115849</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>FOREX BABY BOY HORSE TOY 55X50X25 CM</t>
+          <t>FOREX BABY BLUE WHALE 50X44X25 CM</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -18634,17 +18639,17 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>115844.jpg</t>
+          <t>115849.jpg</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>115847</v>
+        <v>115844</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>FOREX BABY BOY W/HAT DESIGN 53X35X25 CM</t>
+          <t>FOREX BABY BOY HORSE TOY 55X50X25 CM</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -18664,17 +18669,17 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>115847.jpg</t>
+          <t>115844.jpg</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>115845</v>
+        <v>115847</v>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>FOREX BABY BUTTERFLY DESIGN 57X50X25 CM</t>
+          <t>FOREX BABY BOY W/HAT DESIGN 53X35X25 CM</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -18694,17 +18699,17 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>115845.jpg</t>
+          <t>115847.jpg</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>115914</v>
+        <v>115845</v>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>FOREX BABY CAR W/BALLOON DESIGN 48X25X11 CM</t>
+          <t>FOREX BABY BUTTERFLY DESIGN 57X50X25 CM</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -18724,17 +18729,17 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>115914.jpg</t>
+          <t>115845.jpg</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>115885</v>
+        <v>115914</v>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>FOREX BABY DUCK W/HAT DESIGN 40X40X20 CM</t>
+          <t>FOREX BABY CAR W/BALLOON DESIGN 48X25X11 CM</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -18754,17 +18759,17 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>115885.jpg</t>
+          <t>115914.jpg</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>115846</v>
+        <v>115885</v>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>FOREX BABY DUCK W/HAT DESIGN 68X50X25 CM</t>
+          <t>FOREX BABY DUCK W/HAT DESIGN 40X40X20 CM</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -18784,17 +18789,17 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>115846.jpg</t>
+          <t>115885.jpg</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>115848</v>
+        <v>115846</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>FOREX BABY GIRL WITH CLIP DESIGN 53X35X25 CM</t>
+          <t>FOREX BABY DUCK W/HAT DESIGN 68X50X25 CM</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -18814,17 +18819,17 @@
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>115848.jpg</t>
+          <t>115846.jpg</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>115638</v>
+        <v>115848</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>FOREX BABY GIRL ROUND 40CM FLAT WITH HEART 50X37CM</t>
+          <t>FOREX BABY GIRL WITH CLIP DESIGN 53X35X25 CM</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -18844,17 +18849,17 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>115638.jpg</t>
+          <t>115848.jpg</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>115883</v>
+        <v>115638</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>FOREX BABY OCTOPUS DESIGN 50X45X25 CM</t>
+          <t>FOREX BABY GIRL ROUND 40CM FLAT WITH HEART 50X37CM</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -18874,17 +18879,17 @@
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>115883.jpg</t>
+          <t>115638.jpg</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>115884</v>
+        <v>115883</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>FOREX BABY PARACHUTE BALLOON DESIGN 55X45X25 CM</t>
+          <t>FOREX BABY OCTOPUS DESIGN 50X45X25 CM</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -18904,17 +18909,17 @@
       </c>
       <c r="I518" t="inlineStr">
         <is>
-          <t>115884.jpg</t>
+          <t>115883.jpg</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>115606</v>
+        <v>115884</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>FOREX BABY TRAY WHITE WITH BLUE FOREX DESIGN 40X32X33X6 CM</t>
+          <t>FOREX BABY PARACHUTE BALLOON DESIGN 55X45X25 CM</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -18934,17 +18939,17 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>115606.jpg</t>
+          <t>115884.jpg</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>115621</v>
+        <v>115606</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>FOREX BABY TRAY WHITE WITH PINK FOREX DESIGN 40X32X33X6 CM</t>
+          <t>FOREX BABY TRAY WHITE WITH BLUE FOREX DESIGN 40X32X33X6 CM</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -18964,17 +18969,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>115621.jpg</t>
+          <t>115606.jpg</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>110988</v>
+        <v>115621</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>FOREX CAR 55X20X34.6</t>
+          <t>FOREX BABY TRAY WHITE WITH PINK FOREX DESIGN 40X32X33X6 CM</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -18994,17 +18999,17 @@
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>110988.jpg</t>
+          <t>115621.jpg</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>115629</v>
+        <v>110988</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>FOREX DEEP TROLLY BABY BOY 30X25X35 CM</t>
+          <t>FOREX CAR 55X20X34.6</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -19024,17 +19029,17 @@
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>115629.jpg</t>
+          <t>110988.jpg</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>115628</v>
+        <v>115629</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>FOREX DEEP TROLLY BABY GIRL 30X25X35 CM</t>
+          <t>FOREX DEEP TROLLY BABY BOY 30X25X35 CM</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -19054,17 +19059,17 @@
       </c>
       <c r="I523" t="inlineStr">
         <is>
-          <t>115628.jpg</t>
+          <t>115629.jpg</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>110354</v>
+        <v>115628</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>FOREX DUCK TRAY BABY BOY 20X33X36CM</t>
+          <t>FOREX DEEP TROLLY BABY GIRL 30X25X35 CM</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -19084,17 +19089,17 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>110354.png</t>
+          <t>115628.jpg</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>116643</v>
+        <v>110354</v>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY 65x25x5.5CM</t>
+          <t>FOREX DUCK TRAY BABY BOY 20X33X36CM</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -19114,17 +19119,17 @@
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>116643.jpeg</t>
+          <t>110354.png</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>110597</v>
+        <v>116643</v>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY SMALL 34.5X18X2.5CM</t>
+          <t>FOREX OBLONG TRAY 65x25x5.5CM</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -19144,17 +19149,17 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>110597.jpg</t>
+          <t>116643.jpeg</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>116646</v>
+        <v>110597</v>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY W/STICKER 70X40X6 CM</t>
+          <t>FOREX OBLONG TRAY SMALL 34.5X18X2.5CM</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -19174,17 +19179,17 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>116646.jpeg</t>
+          <t>110597.jpg</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>116645</v>
+        <v>116646</v>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY W/STICKER 70X40X15 CM</t>
+          <t>FOREX OBLONG TRAY W/STICKER 70X40X6 CM</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -19204,17 +19209,17 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>116645.jpeg</t>
+          <t>116646.jpeg</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>116648</v>
+        <v>116645</v>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X6 CM</t>
+          <t>FOREX OBLONG TRAY W/STICKER 70X40X15 CM</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -19234,17 +19239,17 @@
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>116648.jpeg</t>
+          <t>116645.jpeg</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>116647</v>
+        <v>116648</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X15 CM</t>
+          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X6 CM</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -19264,17 +19269,17 @@
       </c>
       <c r="I530" t="inlineStr">
         <is>
-          <t>116647.jpeg</t>
+          <t>116648.jpeg</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>115916</v>
+        <v>116647</v>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TROLLEY W/BEE DESIGN 55X30X20 CM</t>
+          <t>FOREX OBLONG TRAY WITH WHITE STICKER 70X40X15 CM</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -19294,17 +19299,17 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>115916.jpg</t>
+          <t>116647.jpeg</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>115939</v>
+        <v>115916</v>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>FOREX ROUND TRAY 37X37X5 CM</t>
+          <t>FOREX OBLONG TROLLEY W/BEE DESIGN 55X30X20 CM</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -19324,17 +19329,17 @@
       </c>
       <c r="I532" t="inlineStr">
         <is>
-          <t>115939.jpg</t>
+          <t>115916.jpg</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>115941</v>
+        <v>115939</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>FOREX ROUND TRAY 40X40X5 CM</t>
+          <t>FOREX ROUND TRAY 37X37X5 CM</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -19354,17 +19359,17 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>115941.jpg</t>
+          <t>115939.jpg</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>117099</v>
+        <v>115941</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>FOREX ROUND TRAY 45X45X5 CM</t>
+          <t>FOREX ROUND TRAY 40X40X5 CM</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -19384,17 +19389,17 @@
       </c>
       <c r="I534" t="inlineStr">
         <is>
-          <t>117099.jpeg</t>
+          <t>115941.jpg</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>110924</v>
+        <v>117099</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>FOREX SCOOTER BABY GIRL/BOY BIG 55X20X34.6CM</t>
+          <t>FOREX ROUND TRAY 45X45X5 CM</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -19414,17 +19419,17 @@
       </c>
       <c r="I535" t="inlineStr">
         <is>
-          <t>110924.jpg</t>
+          <t>117099.jpeg</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>110923</v>
+        <v>110924</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>FOREX SCOOTER BABY GIRL/BOY SMALL 40X17X25CM</t>
+          <t>FOREX SCOOTER BABY GIRL/BOY BIG 55X20X34.6CM</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -19444,17 +19449,17 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>110923.jpg</t>
+          <t>110924.jpg</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>115639</v>
+        <v>110923</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>FOREX STAND BABY BEAR 75X35X15 CM</t>
+          <t>FOREX SCOOTER BABY GIRL/BOY SMALL 40X17X25CM</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -19474,17 +19479,17 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>115639.jpg</t>
+          <t>110923.jpg</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>115627</v>
+        <v>115639</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>FOREX STAND BABY BOY 2 LAYERS 43X31CM 31X31CM H70 CM</t>
+          <t>FOREX STAND BABY BEAR 75X35X15 CM</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -19504,17 +19509,17 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>115627.jpg</t>
+          <t>115639.jpg</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>115626</v>
+        <v>115627</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>FOREX STAND BABY GIRL 2 LAYERS 43X31CM 31X31CM H70 CM</t>
+          <t>FOREX STAND BABY BOY 2 LAYERS 43X31CM 31X31CM H70 CM</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -19534,17 +19539,17 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>115626.jpg</t>
+          <t>115627.jpg</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>112892</v>
+        <v>115626</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>FOREX TRAY 20X17X15CM</t>
+          <t>FOREX STAND BABY GIRL 2 LAYERS 43X31CM 31X31CM H70 CM</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -19564,17 +19569,17 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>112892.jpg</t>
+          <t>115626.jpg</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>115002</v>
+        <v>112892</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY BOY 41X39X4CM</t>
+          <t>FOREX TRAY 20X17X15CM</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -19594,17 +19599,17 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>115002.jpg</t>
+          <t>112892.jpg</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>115001</v>
+        <v>115002</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY GIRL 31X29X4CM</t>
+          <t>FOREX TRAY BABY BOY 41X39X4CM</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -19624,17 +19629,17 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>115001.jpg</t>
+          <t>115002.jpg</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>114999</v>
+        <v>115001</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY GIRL 41X39X4CM</t>
+          <t>FOREX TRAY BABY GIRL 31X29X4CM</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -19654,17 +19659,17 @@
       </c>
       <c r="I543" t="inlineStr">
         <is>
-          <t>114999.jpg</t>
+          <t>115001.jpg</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>115003</v>
+        <v>114999</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>FOREX TRAY BABY GIRL LADDER AND RIBBON 41X39X39CM</t>
+          <t>FOREX TRAY BABY GIRL 41X39X4CM</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -19684,17 +19689,17 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>115003.jpg</t>
+          <t>114999.jpg</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>115635</v>
+        <v>115003</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>FOREX TRAY BOY 30X30X4CM BOARD 28CM</t>
+          <t>FOREX TRAY BABY GIRL LADDER AND RIBBON 41X39X39CM</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -19714,17 +19719,17 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>115635.jpg</t>
+          <t>115003.jpg</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>115623</v>
+        <v>115635</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>FOREX TRAY GIRL 30X30X4CM BOARD 28CM</t>
+          <t>FOREX TRAY BOY 30X30X4CM BOARD 28CM</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -19744,17 +19749,17 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>115632.jpg</t>
+          <t>115635.jpg</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>115630</v>
+        <v>115623</v>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>FOREX TRAY GIRL BOY 30X30X4CM BOARD 20CM</t>
+          <t>FOREX TRAY GIRL 30X30X4CM BOARD 28CM</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -19774,17 +19779,17 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>115630.jpg</t>
+          <t>115632.jpg</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>112889</v>
+        <v>115630</v>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>FOREX TV 25X20X22.5CM</t>
+          <t>FOREX TRAY GIRL BOY 30X30X4CM BOARD 20CM</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -19804,17 +19809,17 @@
       </c>
       <c r="I548" t="inlineStr">
         <is>
-          <t>112889.jpg</t>
+          <t>115630.jpg</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>115858</v>
+        <v>112889</v>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>FOREX W/ACRYLIC OBLONG TRAY 70X40X15 CM</t>
+          <t>FOREX TV 25X20X22.5CM</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -19834,17 +19839,17 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>115858.jpg</t>
+          <t>112889.jpg</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>110502</v>
+        <v>115858</v>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>FOREX WRINTING STAND 25X15CM</t>
+          <t>FOREX W/ACRYLIC OBLONG TRAY 70X40X15 CM</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -19864,17 +19869,17 @@
       </c>
       <c r="I550" t="inlineStr">
         <is>
-          <t>110502.jpg</t>
+          <t>115858.jpg</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>110598</v>
+        <v>110502</v>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY MEDIUM 40X21X2.5CM</t>
+          <t>FOREX WRINTING STAND 25X15CM</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -19890,16 +19895,21 @@
       <c r="G551" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>110502.jpg</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>110599</v>
+        <v>110598</v>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>FOREX OBLONG TRAY LARGE 45X23.5X2.5CM</t>
+          <t>FOREX OBLONG TRAY MEDIUM 40X21X2.5CM</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -19920,11 +19930,11 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>104760</v>
+        <v>110599</v>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>FLAT FOREX WHITE 29.729.71CM</t>
+          <t>FOREX OBLONG TRAY LARGE 45X23.5X2.5CM</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -19940,21 +19950,16 @@
       <c r="G553" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
-        </is>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>104760.png</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>104761</v>
+        <v>104760</v>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>FLAT FOREX WHITE 35.35.1CM</t>
+          <t>FLAT FOREX WHITE 29.729.71CM</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -19974,17 +19979,17 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>104761.PNG</t>
+          <t>104760.png</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>104762</v>
+        <v>104761</v>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>FLAT FOREX WHITE 39.739.71CM</t>
+          <t>FLAT FOREX WHITE 35.35.1CM</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -20004,17 +20009,17 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>104762.png</t>
+          <t>104761.PNG</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>104763</v>
+        <v>104762</v>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>FLAT FOREX WHITE 49.749.71CM</t>
+          <t>FLAT FOREX WHITE 39.739.71CM</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -20030,201 +20035,201 @@
       <c r="G556" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>104762.png</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
+        <v>104763</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>FLAT FOREX WHITE 49.749.71CM</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Forex Stands</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Forex</t>
+        </is>
+      </c>
+      <c r="G557" s="18" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
         <v>109676</v>
       </c>
-      <c r="B557" t="inlineStr">
+      <c r="B558" t="inlineStr">
         <is>
           <t>FOREX BABY BOY CAR 40X22X18CM</t>
         </is>
       </c>
-      <c r="C557" t="inlineStr">
+      <c r="C558" t="inlineStr">
         <is>
           <t>Forex Stands</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
+      <c r="D558" t="inlineStr">
         <is>
           <t>Forex</t>
         </is>
       </c>
-      <c r="G557" s="18" t="inlineStr">
+      <c r="G558" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="I557" t="inlineStr">
+      <c r="I558" t="inlineStr">
         <is>
           <t>109676.jpg</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" s="21" t="inlineStr">
+    <row r="559">
+      <c r="A559" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">117632 </t>
         </is>
       </c>
-      <c r="B558" t="inlineStr">
+      <c r="B559" t="inlineStr">
         <is>
           <t>Premium Wafer Cerelak JAR</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
+      <c r="C559" t="inlineStr">
         <is>
           <t>Wafer</t>
         </is>
       </c>
-      <c r="D558" s="15" t="inlineStr">
+      <c r="D559" s="15" t="inlineStr">
         <is>
           <t>Jars</t>
         </is>
       </c>
-      <c r="G558" s="18" t="inlineStr">
+      <c r="G559" s="18" t="inlineStr">
         <is>
           <t>PCS</t>
         </is>
       </c>
-      <c r="I558" t="inlineStr">
+      <c r="I559" t="inlineStr">
         <is>
           <t>custom-premium-wafer-cerelak-jar.jpg</t>
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="n">
+    <row r="560" customFormat="1" s="22">
+      <c r="A560" t="n">
         <v>107840</v>
       </c>
-      <c r="B559" t="inlineStr">
+      <c r="B560" t="inlineStr">
         <is>
           <t>Dragee box mix</t>
         </is>
       </c>
-      <c r="C559" t="inlineStr">
+      <c r="C560" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr">
+      <c r="D560" t="inlineStr">
         <is>
           <t>Secondary items</t>
         </is>
       </c>
-      <c r="I559" t="inlineStr">
+      <c r="I560" t="inlineStr">
         <is>
           <t>custom-dragee-box-mix.jpg</t>
         </is>
       </c>
     </row>
-    <row r="560" customFormat="1" s="22">
-      <c r="A560" s="22" t="n">
+    <row r="561">
+      <c r="A561" s="22" t="n">
         <v>100303</v>
       </c>
-      <c r="B560" s="22" t="inlineStr">
+      <c r="B561" s="22" t="inlineStr">
         <is>
           <t>PREMIUM ITALIAN WRAPPED DARK ORANGE KG</t>
         </is>
       </c>
-      <c r="C560" s="23" t="inlineStr">
+      <c r="C561" s="23" t="inlineStr">
         <is>
           <t>Special</t>
         </is>
       </c>
-      <c r="D560" s="23" t="inlineStr">
+      <c r="D561" s="23" t="inlineStr">
         <is>
           <t>Secondary items</t>
         </is>
       </c>
-      <c r="G560" s="22" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="H560" s="22" t="n">
+      <c r="G561" s="22" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="H561" s="22" t="n">
         <v>168</v>
       </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>111175.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="n">
-        <v>100069</v>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>TAMRIYA BOX 900G- PCS</t>
-        </is>
-      </c>
-      <c r="C561" s="23" t="inlineStr">
-        <is>
-          <t>Special</t>
-        </is>
-      </c>
-      <c r="D561" s="23" t="inlineStr">
-        <is>
-          <t>Secondary items</t>
-        </is>
-      </c>
-      <c r="G561" s="18" t="inlineStr">
-        <is>
-          <t>PCS</t>
-        </is>
-      </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>custom-tamriya-box-900g-pcs.jpg</t>
+          <t>custom-premium-italian-wrapped-dark-orange-kg.jpg</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>100382</v>
+        <v>100069</v>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>PREMIUM BELGIUM WRAPPED BROWN GOLDEN BISCUIT KG</t>
-        </is>
-      </c>
-      <c r="C562" s="15" t="inlineStr">
-        <is>
-          <t>Belgium wrapped</t>
-        </is>
-      </c>
-      <c r="D562" s="2" t="inlineStr">
-        <is>
-          <t>Belgium chocolate</t>
+          <t>TAMRIYA BOX 900G- PCS</t>
+        </is>
+      </c>
+      <c r="C562" s="23" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="D562" s="23" t="inlineStr">
+        <is>
+          <t>Secondary items</t>
         </is>
       </c>
       <c r="G562" s="18" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>PCS</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>custom-premium-belgium-wrapped-brown-golden-biscuit-kg.jpg</t>
+          <t>custom-tamriya-box-900g-pcs.jpg</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>100414</v>
+        <v>100382</v>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>PREMIUM BELGIUM WRAPPED BROWN CORNFLAKES KG</t>
-        </is>
-      </c>
-      <c r="C563" s="2" t="inlineStr">
-        <is>
-          <t>Open chocolalate</t>
+          <t>PREMIUM BELGIUM WRAPPED BROWN GOLDEN BISCUIT KG</t>
+        </is>
+      </c>
+      <c r="C563" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
@@ -20232,29 +20237,29 @@
           <t>Belgium chocolate</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr">
+      <c r="G563" s="18" t="inlineStr">
         <is>
           <t>KG</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>custom-premium-belgium-wrapped-brown-cornflakes-kg.jpg</t>
+          <t>custom-premium-belgium-wrapped-brown-golden-biscuit-kg.jpg</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>100382</v>
+        <v>100414</v>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>PREMIUM BELGIUM WRAPPED BROWN COTTON CANDY KG</t>
-        </is>
-      </c>
-      <c r="C564" s="15" t="inlineStr">
-        <is>
-          <t>Belgium wrapped</t>
+          <t>PREMIUM BELGIUM WRAPPED BROWN CORNFLAKES KG</t>
+        </is>
+      </c>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>Open chocolalate</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
@@ -20269,35 +20274,65 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>custom-premium-belgium-wrapped-brown-cotton-candy-kg.jpg</t>
+          <t>custom-premium-belgium-wrapped-brown-cornflakes-kg.jpg</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
+        <v>100382</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>PREMIUM BELGIUM WRAPPED BROWN COTTON CANDY KG</t>
+        </is>
+      </c>
+      <c r="C565" s="15" t="inlineStr">
+        <is>
+          <t>Belgium wrapped</t>
+        </is>
+      </c>
+      <c r="D565" s="2" t="inlineStr">
+        <is>
+          <t>Belgium chocolate</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>custom-premium-belgium-wrapped-brown-cotton-candy-kg.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
         <v>108656</v>
       </c>
-      <c r="B565" t="inlineStr">
+      <c r="B566" t="inlineStr">
         <is>
           <t>PREMIUM BELGIUM WRAPPED BROWN ROUND DIRHAM PLAIN CHOCOLATE WITH CHOCOLATE PRINT KG</t>
         </is>
       </c>
-      <c r="C565" s="15" t="inlineStr">
+      <c r="C566" s="15" t="inlineStr">
         <is>
           <t>Customized</t>
         </is>
       </c>
-      <c r="D565" s="2" t="inlineStr">
+      <c r="D566" s="2" t="inlineStr">
         <is>
           <t>Belgium chocolate</t>
         </is>
       </c>
-      <c r="G565" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="I565" t="inlineStr">
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
         <is>
           <t>custom-premium-belgium-wrapped-brown-round-dirham-plain-chocolate-with-chocolate-print-kg.jpg</t>
         </is>
